--- a/CompanyPortal/docs/10_requirements/要件定義.xlsx
+++ b/CompanyPortal/docs/10_requirements/要件定義.xlsx
@@ -5,23 +5,21 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ドンウン\Desktop\プロジェクト整理フォルダ\要件定義\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OWNER\Documents\ProjectFolder\CompanyPortal\CompanyPortal\docs\10_requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6757C4BE-187C-42D2-A169-2A2B59F17F14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F951E6-6863-467A-8037-1482A6EBE56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25CA8C25-5F49-4505-BACD-CA03491A7370}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{25CA8C25-5F49-4505-BACD-CA03491A7370}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="README" sheetId="6" r:id="rId2"/>
     <sheet name="要件定義" sheetId="4" r:id="rId3"/>
-    <sheet name="テンプレート" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">README!$A$1:$AO$67</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">テンプレート!$A$1:$AO$71</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">要件定義!$A$1:$AO$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">README!$A$1:$AO$66</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">要件定義!$A$1:$CG$91</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="96">
   <si>
     <t>모든 직원이 쓰되, 각각 관리자 권한의 페이지, 일반 말단 직원의 권한, 회계팀만 가지고 있는 권한도 있거나 그런거지. 거래처와 한 거래를 기록하는 페이지도 있고 사원 관리를 하는 HR의 권한 페이지도 있고, 뭐 이런저런거 있어. 그리고 그리드를 만들고, 모든 사원이 즉시 엑셀을 사용할 수 있는 스프레드 시트 등도 있고, 엑셀이다보니까 출력기능도 만들거나, 그런 거지. 뭐가 가장 불편한가는 뭘 묻는 건지 잘 모르겠어. 아예 기존의 어플이라던지 웹이 있던게 아니라서 보수 개발을 하는게 아니야. 그래서 뭐가 가장 불편한가라는 거에 대답하긴 어려워. 시스템 도입 후 뭐가 좋아져야 하는가도 그렇고. 근데 만약 내가 진짜 직원으로서 고민을 해본다면, 보통 직원들은 엑셀 파일을 통해서 다양한 서류나 정보를 입출력을 해. 근데 그 엑셀 파일을 보내고 받고 열고 저장하고, 이런 것이 너무 번거롭다보니까 한 번에 모두가 이용할 수 있는 스프레드시트를 개발하고자 한다? 라고 볼 수 있겠네. 물론 실제로 이런 모델이 있기도 하지만, 어쩄든 난 내 스스로의 프로젝트로 커리어상향을 시키는 것일 뿐이니까. 그리고 단순 스프레드 시트뿐이라기보다는 어찌되었든, 사내 시스템이다보니까 아까 말한 것처럼, 거래처 등록이나 거래 내역 추가 조회 삭제 등등, 서면으로 기록을 남기는 것도 어려울 뿐더러, 엑셀 파일도 다양한 직원들이 확인을 하려면 어려 과정을 거쳐야 한다는 번거로움을 줄이기 위한 것이 사내 시스템, 사내 프로그램이잖아. 그래서 그런 거지. 그래서 시스템 도입을 하게 되면 업무 시간 감소로 효율성 극대화와 기록 저장 등의 간소화, 다양한 부서들이 한 웹앱을 이용하는 데이터 통합도 있겠네.</t>
   </si>
@@ -504,10 +502,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>勤怠管理ページは、自分の勤怠を記載するページで、各部署長に権限があります。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>各</t>
     </r>
@@ -561,6 +555,110 @@
   </si>
   <si>
     <t>取引ページは、取引先と取引内訳に関する管理し、営業部に権限があります。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>各部署別ダッシュボードページは、各部署の朝会、タスク、TODO等があり、権限条件はありません。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本的にIT部署は全てのページに権限があり、開発、及び保守のため、開発ページが外部におき、全社員・全部署の権限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>アクセスができます。ただし、個人情報は流用せず他の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>データベースを使います。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사내 시스템 페이지 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 각부서별 대시보드 페이지 중 기능 : 공유 스프레드시트, 공유 캘린더, 공유 TODO, 채팅기능 제작</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근태관리 페이지 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사원 관리 페이지 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 전사원의 인사고과와 입사일, 근태기록, 휴직기록, 징계기록, 발령등록, 부서이동, 승진 등 등록 및 열람 가능
+각 부서장들이 작성한 인사고과에 반영해 승진여부를 묻는다.
+승진 결정나면 승진 사유서를 작성한다. 작성하고 등록하면 경리부 승진 담당자에게 메일 발송한다. 메일 수신시 사내 개인 메신저로 연락이 온다.
+경리부와 함께 회의에 들어가며 최종 연봉을 정한다.
+승진 사유서와 최종 연봉을 승진 결재서에 작성한다.
+사내 시스템을 통해 주임, 과장, 부장, ... , 사장에게 결재를 받는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>거래 페이지 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>施設備品管理ページは、施設利用、及び備品予約申し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="MS Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>込</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans KR"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>み、経理部に権限があります。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 거래처 등록 및 삭제, 거래 등록 및 취소, 거래처대장, 거래내역, 거래개정
+거래 등록을 하고 결재가 완료되면 경리부에 메일 발송한다. 메일 수신시 사내 개인 메신저로 연락이 온다.
+거래의 결재는 영업부장까지 이루어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 출퇴근 간단 등록, 자주 사용하는 출퇴근시간 복사(리스트로 총 3개까지)
+로그인하면 세션을 통해 자동 출근 기록. 퇴근은 세션 관계 없이 꼭 버튼 클릭.
+출퇴근 시간 수정 가능.
+근태 등록이 완료되면 다음 결재자에게 리시테아에 부원의 근태 등록완료 표시가 뜬다.
+근태 결재는 총 등록, 심사, 승인으로 이루어지며, 심사는 해당 부서의 과장이, 승인은 부장이 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시설 비품 관리 페이지 구상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-&gt; 회사에서 이루어지는 모든 금전적인 움직임을 담당한다. 
+각각의 부서 내에서 비품구매를 요청을 할 수 있다. 각부서주임~부장까지 등록 권한이 있다.
+각 부서에서 이러한 요청서를 올리면, 이를 토대로 결재를 한다. 결재는 대개 부장까지만 이루어지나, 단순 비품이 아닌 특수 및 대량 비품의 경우 사장까지 결재가 이루어진다.
+비품과는 다르게 시설에서 발생하는 비용의 경우 모든 결재가 사장까지 이루어진다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -605,132 +703,218 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>なシステムにアクセスできます。メニューからは、お知らせページ、勤怠管理ページ、各</t>
+      <t>なシステムにアクセスできます。</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>様</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>式ライブラリページ、社員管理ページ、取引ページ、施設備品管理ページ、各部署別ダッシュボードページがあります。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>各部署別ダッシュボードページは、各部署の朝会、タスク、TODO等があり、権限条件はありません。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基本的にIT部署は全てのページに権限があり、開発、及び保守のため、開発ページが外部におき、全社員・全部署の権限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>アクセスができます。ただし、個人情報は流用せず他の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>データベースを使います。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사내 시스템 페이지 구상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; 각부서별 대시보드 페이지 중 기능 : 공유 스프레드시트, 공유 캘린더, 공유 TODO, 채팅기능 제작</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>근태관리 페이지 구상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>사원 관리 페이지 구상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; 전사원의 인사고과와 입사일, 근태기록, 휴직기록, 징계기록, 발령등록, 부서이동, 승진 등 등록 및 열람 가능
-각 부서장들이 작성한 인사고과에 반영해 승진여부를 묻는다.
-승진 결정나면 승진 사유서를 작성한다. 작성하고 등록하면 경리부 승진 담당자에게 메일 발송한다. 메일 수신시 사내 개인 메신저로 연락이 온다.
-경리부와 함께 회의에 들어가며 최종 연봉을 정한다.
-승진 사유서와 최종 연봉을 승진 결재서에 작성한다.
-사내 시스템을 통해 주임, 과장, 부장, ... , 사장에게 결재를 받는다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래 페이지 구상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>施設備品管理ページは、施設利用、及び備品予約申し</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>込</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans KR"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>み、経理部に権限があります。</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; 거래처 등록 및 삭제, 거래 등록 및 취소, 거래처대장, 거래내역, 거래개정
-거래 등록을 하고 결재가 완료되면 경리부에 메일 발송한다. 메일 수신시 사내 개인 메신저로 연락이 온다.
-거래의 결재는 영업부장까지 이루어진다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; 출퇴근 간단 등록, 자주 사용하는 출퇴근시간 복사(리스트로 총 3개까지)
-로그인하면 세션을 통해 자동 출근 기록. 퇴근은 세션 관계 없이 꼭 버튼 클릭.
-출퇴근 시간 수정 가능.
-근태 등록이 완료되면 다음 결재자에게 리시테아에 부원의 근태 등록완료 표시가 뜬다.
-근태 결재는 총 등록, 심사, 승인으로 이루어지며, 심사는 해당 부서의 과장이, 승인은 부장이 한다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시설 비품 관리 페이지 구상</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>-&gt; 회사에서 이루어지는 모든 금전적인 움직임을 담당한다. 
-각각의 부서 내에서 비품구매를 요청을 할 수 있다. 각부서주임~부장까지 등록 권한이 있다.
-각 부서에서 이러한 요청서를 올리면, 이를 토대로 결재를 한다. 결재는 대개 부장까지만 이루어지나, 단순 비품이 아닌 특수 및 대량 비품의 경우 사장까지 결재가 이루어진다.
-비품과는 다르게 시설에서 발생하는 비용의 경우 모든 결재가 사장까지 이루어진다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理ページ、各部署別ダッシュボードページがあります。</t>
+  </si>
+  <si>
+    <t>作成日：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>作成者：</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>チェ ドンウン</t>
+  </si>
+  <si>
+    <t>NO</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1st</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2nd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3rd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4th</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5th</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メニュー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>区分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>状況</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受入条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制約条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>変更内容・参考事項</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>社内システム開発プロジェクト_要件定義</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログイン画面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログインページ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メインメニューページ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ログイン</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>パスワード探し</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>管理者へ送信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新規</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知らせ画面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メッセージ送信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>カテゴリー</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>アップロード</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ダウンロード</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>添付ファイル</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知らせ詳細</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知らせ登録</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>お知らせ一覧</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ページング</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>削除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>権限：自分</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>権限：各部署長</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>権限：IT部署</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IT部署へパスワード問い合わせメッセージを送信
+パスワード変更付与は管理者により</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>保留</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是正要請</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月別確認</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>承認者登録</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>全社員</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>メニューからは、お知らせページ、勤務管理ページ、各様式ライブラリページ、社員管理ページ、取引ページ、施設備品</t>
+  </si>
+  <si>
+    <t>勤務管理ページは、自分の勤務を記載するページで、各部署長に権限があります。</t>
+  </si>
+  <si>
+    <t>勤務管理画面</t>
+  </si>
+  <si>
+    <t>勤務登録</t>
+  </si>
+  <si>
+    <t>勤務一覧</t>
+  </si>
+  <si>
+    <t>各社員の勤務確認</t>
+  </si>
+  <si>
+    <t>権限：全社員
+自分の勤務承認者を選択。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -738,7 +922,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy/mm/dd;@"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -823,16 +1010,36 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -920,13 +1127,145 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -943,7 +1282,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -954,7 +1311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
@@ -969,29 +1326,125 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -999,6 +1452,12 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF363636"/>
+      <color rgb="FF615A62"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1308,7 +1767,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BFFCA66-92E5-42BD-8C54-4FC8295AF3EC}">
   <dimension ref="A3:E27"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="79.5" style="1" customWidth="1"/>
     <col min="3" max="3" width="72.625" customWidth="1"/>
@@ -1316,14 +1775,14 @@
     <col min="5" max="5" width="35.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+    </row>
+    <row r="4" spans="1:5" ht="18.75">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1334,7 +1793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="379.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="379.5">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1348,7 +1807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="409.5">
       <c r="A6" s="1" t="s">
         <v>0</v>
       </c>
@@ -1359,7 +1818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="409.5">
       <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
@@ -1367,7 +1826,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="409.5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="409.5">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -1375,54 +1834,54 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1">
       <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="33">
+      <c r="A19" s="9" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="33" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+    <row r="21" spans="1:1" ht="99">
+      <c r="A21" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+    <row r="23" spans="1:1" ht="132">
+      <c r="A23" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="99" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="s">
+    <row r="24" spans="1:1">
+      <c r="A24" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="66">
+      <c r="A25" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="82.5">
+      <c r="A27" s="9" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" ht="132" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" ht="66" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" ht="82.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1436,443 +1895,543 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CE075E-7E7E-4611-9139-689A3F1C0ED1}">
-  <dimension ref="C2:AM32"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="C2:AM40"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="16.5"/>
   <sheetData>
-    <row r="2" spans="3:39" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="14" t="s">
+    <row r="2" spans="3:39" ht="17.25" thickBot="1"/>
+    <row r="3" spans="3:39" ht="17.25" thickTop="1">
+      <c r="C3" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-      <c r="AD3" s="6"/>
-      <c r="AE3" s="6"/>
-      <c r="AF3" s="6"/>
-      <c r="AG3" s="6"/>
-      <c r="AH3" s="6"/>
-      <c r="AI3" s="6"/>
-      <c r="AJ3" s="6"/>
-      <c r="AK3" s="6"/>
-      <c r="AL3" s="6"/>
-      <c r="AM3" s="7"/>
-    </row>
-    <row r="4" spans="3:39" x14ac:dyDescent="0.3">
-      <c r="C4" s="8"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
-      <c r="AB4" s="9"/>
-      <c r="AC4" s="9"/>
-      <c r="AD4" s="9"/>
-      <c r="AE4" s="9"/>
-      <c r="AF4" s="9"/>
-      <c r="AG4" s="9"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="9"/>
-      <c r="AJ4" s="9"/>
-      <c r="AK4" s="9"/>
-      <c r="AL4" s="9"/>
-      <c r="AM4" s="10"/>
-    </row>
-    <row r="5" spans="3:39" x14ac:dyDescent="0.3">
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="9"/>
-      <c r="AE5" s="9"/>
-      <c r="AF5" s="9"/>
-      <c r="AG5" s="9"/>
-      <c r="AH5" s="9"/>
-      <c r="AI5" s="9"/>
-      <c r="AJ5" s="9"/>
-      <c r="AK5" s="9"/>
-      <c r="AL5" s="9"/>
-      <c r="AM5" s="10"/>
-    </row>
-    <row r="6" spans="3:39" x14ac:dyDescent="0.3">
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9"/>
-      <c r="K6" s="9"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="9"/>
-      <c r="AE6" s="9"/>
-      <c r="AF6" s="9"/>
-      <c r="AG6" s="9"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="9"/>
-      <c r="AJ6" s="9"/>
-      <c r="AK6" s="9"/>
-      <c r="AL6" s="9"/>
-      <c r="AM6" s="10"/>
-    </row>
-    <row r="7" spans="3:39" x14ac:dyDescent="0.3">
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="9"/>
-      <c r="R7" s="9"/>
-      <c r="S7" s="9"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="9"/>
-      <c r="AE7" s="9"/>
-      <c r="AF7" s="9"/>
-      <c r="AG7" s="9"/>
-      <c r="AH7" s="9"/>
-      <c r="AI7" s="9"/>
-      <c r="AJ7" s="9"/>
-      <c r="AK7" s="9"/>
-      <c r="AL7" s="9"/>
-      <c r="AM7" s="10"/>
-    </row>
-    <row r="8" spans="3:39" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C8" s="11"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
-      <c r="T8" s="12"/>
-      <c r="U8" s="12"/>
-      <c r="V8" s="12"/>
-      <c r="W8" s="12"/>
-      <c r="X8" s="12"/>
-      <c r="Y8" s="12"/>
-      <c r="Z8" s="12"/>
-      <c r="AA8" s="12"/>
-      <c r="AB8" s="12"/>
-      <c r="AC8" s="12"/>
-      <c r="AD8" s="12"/>
-      <c r="AE8" s="12"/>
-      <c r="AF8" s="12"/>
-      <c r="AG8" s="12"/>
-      <c r="AH8" s="12"/>
-      <c r="AI8" s="12"/>
-      <c r="AJ8" s="12"/>
-      <c r="AK8" s="12"/>
-      <c r="AL8" s="12"/>
-      <c r="AM8" s="13"/>
-    </row>
-    <row r="9" spans="3:39" ht="17.25" thickTop="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="17" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="12"/>
+      <c r="Z3" s="12"/>
+      <c r="AA3" s="12"/>
+      <c r="AB3" s="12"/>
+      <c r="AC3" s="12"/>
+      <c r="AD3" s="12"/>
+      <c r="AE3" s="12"/>
+      <c r="AF3" s="12"/>
+      <c r="AG3" s="12"/>
+      <c r="AH3" s="12"/>
+      <c r="AI3" s="12"/>
+      <c r="AJ3" s="12"/>
+      <c r="AK3" s="12"/>
+      <c r="AL3" s="12"/>
+      <c r="AM3" s="13"/>
+    </row>
+    <row r="4" spans="3:39">
+      <c r="C4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+      <c r="O4" s="15"/>
+      <c r="P4" s="15"/>
+      <c r="Q4" s="15"/>
+      <c r="R4" s="15"/>
+      <c r="S4" s="15"/>
+      <c r="T4" s="15"/>
+      <c r="U4" s="15"/>
+      <c r="V4" s="15"/>
+      <c r="W4" s="15"/>
+      <c r="X4" s="15"/>
+      <c r="Y4" s="15"/>
+      <c r="Z4" s="15"/>
+      <c r="AA4" s="15"/>
+      <c r="AB4" s="15"/>
+      <c r="AC4" s="15"/>
+      <c r="AD4" s="15"/>
+      <c r="AE4" s="15"/>
+      <c r="AF4" s="15"/>
+      <c r="AG4" s="15"/>
+      <c r="AH4" s="15"/>
+      <c r="AI4" s="15"/>
+      <c r="AJ4" s="15"/>
+      <c r="AK4" s="15"/>
+      <c r="AL4" s="15"/>
+      <c r="AM4" s="16"/>
+    </row>
+    <row r="5" spans="3:39">
+      <c r="C5" s="14"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="15"/>
+      <c r="Z5" s="15"/>
+      <c r="AA5" s="15"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="15"/>
+      <c r="AD5" s="15"/>
+      <c r="AE5" s="15"/>
+      <c r="AF5" s="15"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="15"/>
+      <c r="AJ5" s="15"/>
+      <c r="AK5" s="15"/>
+      <c r="AL5" s="15"/>
+      <c r="AM5" s="16"/>
+    </row>
+    <row r="6" spans="3:39">
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="15"/>
+      <c r="O6" s="15"/>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="15"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="15"/>
+      <c r="U6" s="15"/>
+      <c r="V6" s="15"/>
+      <c r="W6" s="15"/>
+      <c r="X6" s="15"/>
+      <c r="Y6" s="15"/>
+      <c r="Z6" s="15"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="15"/>
+      <c r="AC6" s="15"/>
+      <c r="AD6" s="15"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="15"/>
+      <c r="AG6" s="15"/>
+      <c r="AH6" s="15"/>
+      <c r="AI6" s="15"/>
+      <c r="AJ6" s="15"/>
+      <c r="AK6" s="15"/>
+      <c r="AL6" s="15"/>
+      <c r="AM6" s="16"/>
+    </row>
+    <row r="7" spans="3:39">
+      <c r="C7" s="14"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="15"/>
+      <c r="O7" s="15"/>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="15"/>
+      <c r="R7" s="15"/>
+      <c r="S7" s="15"/>
+      <c r="T7" s="15"/>
+      <c r="U7" s="15"/>
+      <c r="V7" s="15"/>
+      <c r="W7" s="15"/>
+      <c r="X7" s="15"/>
+      <c r="Y7" s="15"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="15"/>
+      <c r="AC7" s="15"/>
+      <c r="AD7" s="15"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="15"/>
+      <c r="AH7" s="15"/>
+      <c r="AI7" s="15"/>
+      <c r="AJ7" s="15"/>
+      <c r="AK7" s="15"/>
+      <c r="AL7" s="15"/>
+      <c r="AM7" s="16"/>
+    </row>
+    <row r="8" spans="3:39" ht="17.25" thickBot="1">
+      <c r="C8" s="17"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="18"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18"/>
+      <c r="S8" s="18"/>
+      <c r="T8" s="18"/>
+      <c r="U8" s="18"/>
+      <c r="V8" s="18"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="18"/>
+      <c r="Y8" s="18"/>
+      <c r="Z8" s="18"/>
+      <c r="AA8" s="18"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
+      <c r="AD8" s="18"/>
+      <c r="AE8" s="18"/>
+      <c r="AF8" s="18"/>
+      <c r="AG8" s="18"/>
+      <c r="AH8" s="18"/>
+      <c r="AI8" s="18"/>
+      <c r="AJ8" s="18"/>
+      <c r="AK8" s="18"/>
+      <c r="AL8" s="18"/>
+      <c r="AM8" s="19"/>
+    </row>
+    <row r="9" spans="3:39" ht="17.25" thickTop="1"/>
+    <row r="11" spans="3:39" ht="18.75" customHeight="1">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="20"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20"/>
+      <c r="AB11" s="20"/>
+      <c r="AC11" s="20"/>
+      <c r="AD11" s="20"/>
+      <c r="AE11" s="20"/>
+      <c r="AF11" s="20"/>
+      <c r="AG11" s="20"/>
+      <c r="AH11" s="20"/>
+      <c r="AI11" s="20"/>
+      <c r="AJ11" s="20"/>
+      <c r="AK11" s="20"/>
+      <c r="AL11" s="20"/>
+    </row>
+    <row r="12" spans="3:39" ht="18.75">
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="21"/>
+      <c r="V12" s="21"/>
+      <c r="W12" s="21"/>
+      <c r="X12" s="21"/>
+      <c r="Y12" s="21"/>
+      <c r="Z12" s="21"/>
+      <c r="AA12" s="21"/>
+      <c r="AB12" s="21"/>
+      <c r="AC12" s="21"/>
+      <c r="AD12" s="21"/>
+      <c r="AE12" s="21"/>
+      <c r="AF12" s="21"/>
+      <c r="AG12" s="21"/>
+      <c r="AH12" s="21"/>
+      <c r="AI12" s="21"/>
+      <c r="AJ12" s="21"/>
+      <c r="AK12" s="21"/>
+      <c r="AL12" s="21"/>
+    </row>
+    <row r="13" spans="3:39" ht="18.75" customHeight="1">
+      <c r="D13" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="17"/>
-      <c r="P11" s="17"/>
-      <c r="Q11" s="17"/>
-      <c r="R11" s="17"/>
-      <c r="S11" s="17"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="17"/>
-      <c r="V11" s="17"/>
-      <c r="W11" s="17"/>
-      <c r="X11" s="17"/>
-      <c r="Y11" s="17"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="17"/>
-      <c r="AB11" s="17"/>
-      <c r="AC11" s="17"/>
-      <c r="AD11" s="17"/>
-      <c r="AE11" s="17"/>
-      <c r="AF11" s="17"/>
-      <c r="AG11" s="17"/>
-      <c r="AH11" s="17"/>
-      <c r="AI11" s="17"/>
-      <c r="AJ11" s="17"/>
-      <c r="AK11" s="17"/>
-      <c r="AL11" s="17"/>
-    </row>
-    <row r="12" spans="3:39" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D12" s="15" t="s">
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="20"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20"/>
+      <c r="AB13" s="20"/>
+      <c r="AC13" s="20"/>
+      <c r="AD13" s="20"/>
+      <c r="AE13" s="20"/>
+      <c r="AF13" s="20"/>
+      <c r="AG13" s="20"/>
+      <c r="AH13" s="20"/>
+      <c r="AI13" s="20"/>
+      <c r="AJ13" s="20"/>
+      <c r="AK13" s="20"/>
+      <c r="AL13" s="20"/>
+    </row>
+    <row r="14" spans="3:39" ht="18.75">
+      <c r="D14" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
-      <c r="AL12" s="15"/>
-    </row>
-    <row r="13" spans="3:39" x14ac:dyDescent="0.3">
-      <c r="D13" s="16" t="s">
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+    </row>
+    <row r="15" spans="3:39">
+      <c r="D15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16"/>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-      <c r="AB13" s="16"/>
-      <c r="AC13" s="16"/>
-      <c r="AD13" s="16"/>
-      <c r="AE13" s="16"/>
-      <c r="AF13" s="16"/>
-      <c r="AG13" s="16"/>
-      <c r="AH13" s="16"/>
-      <c r="AI13" s="16"/>
-      <c r="AJ13" s="16"/>
-      <c r="AK13" s="16"/>
-      <c r="AL13" s="16"/>
-    </row>
-    <row r="15" spans="3:39" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="D15" s="18" t="s">
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+      <c r="AA15" s="5"/>
+      <c r="AB15" s="5"/>
+      <c r="AC15" s="5"/>
+      <c r="AD15" s="5"/>
+      <c r="AE15" s="5"/>
+      <c r="AF15" s="5"/>
+      <c r="AG15" s="5"/>
+      <c r="AH15" s="5"/>
+      <c r="AI15" s="5"/>
+      <c r="AJ15" s="5"/>
+      <c r="AK15" s="5"/>
+      <c r="AL15" s="5"/>
+    </row>
+    <row r="17" spans="4:6" ht="18">
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="4:6" ht="18.75">
+      <c r="D18" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="3:39" ht="18" x14ac:dyDescent="0.3">
-      <c r="D16" s="19" t="s">
+    <row r="19" spans="4:6" ht="18">
+      <c r="D19" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="D17" t="s">
+    <row r="20" spans="4:6" ht="18">
+      <c r="D20" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F19" s="20" t="s">
+    <row r="22" spans="4:6" ht="18">
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="4:6" ht="18">
+      <c r="F23" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" ht="18">
+      <c r="F24" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" ht="18">
+      <c r="F25" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" ht="18">
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="4:6" ht="18">
+      <c r="F27" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="18">
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="4:6" ht="18">
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="4:6" ht="18">
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="4:6" ht="18">
+      <c r="F31" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" ht="18">
+      <c r="F32" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" ht="18">
+      <c r="F33" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" ht="18">
+      <c r="F34" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" ht="18">
+      <c r="F35" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" ht="18">
+      <c r="F36" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" ht="18">
+      <c r="F37" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="6:6" ht="18">
+      <c r="F39" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F20" s="19"/>
-    </row>
-    <row r="21" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F21" s="19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F23" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F24" s="19" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F25" s="19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F26" s="19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F27" s="19" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F28" s="19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F29" s="19" t="s">
+    <row r="40" spans="6:6" ht="18">
+      <c r="F40" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F31" s="19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6" ht="18" x14ac:dyDescent="0.3">
-      <c r="F32" t="s">
-        <v>31</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="C3:AM8"/>
     <mergeCell ref="D11:AL11"/>
     <mergeCell ref="D12:AL12"/>
     <mergeCell ref="D13:AL13"/>
+    <mergeCell ref="D14:AL14"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1882,25 +2441,4143 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AC8068-FBB9-4CAB-B9B3-430B3C2AB563}">
-  <dimension ref="H1:P1"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetPr>
+    <pageSetUpPr autoPageBreaks="0"/>
+  </sheetPr>
+  <dimension ref="B2:CF91"/>
+  <sheetFormatPr defaultColWidth="2.375" defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="16384" width="2.375" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:84">
+      <c r="B2" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="41"/>
+      <c r="S2" s="41"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="41"/>
+      <c r="V2" s="41"/>
+      <c r="W2" s="41"/>
+      <c r="X2" s="41"/>
+      <c r="Y2" s="41"/>
+      <c r="Z2" s="41"/>
+      <c r="AA2" s="41"/>
+      <c r="AB2" s="41"/>
+      <c r="AC2" s="41"/>
+      <c r="AD2" s="41"/>
+      <c r="AE2" s="41"/>
+      <c r="AF2" s="41"/>
+      <c r="AG2" s="41"/>
+      <c r="AH2" s="41"/>
+      <c r="AI2" s="41"/>
+      <c r="AJ2" s="41"/>
+      <c r="AK2" s="41"/>
+      <c r="AL2" s="41"/>
+      <c r="AM2" s="41"/>
+      <c r="AN2" s="41"/>
+      <c r="AO2" s="41"/>
+      <c r="AP2" s="41"/>
+      <c r="AQ2" s="41"/>
+    </row>
+    <row r="4" spans="2:84">
+      <c r="B4" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="32">
+        <v>46166</v>
+      </c>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+    </row>
+    <row r="5" spans="2:84">
+      <c r="B5" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="24"/>
+      <c r="AI5" s="24"/>
+      <c r="AJ5" s="24"/>
+      <c r="AK5" s="24"/>
+      <c r="AL5" s="24"/>
+      <c r="AM5" s="24"/>
+      <c r="AN5" s="24"/>
+      <c r="AO5" s="24"/>
+      <c r="AP5" s="24"/>
+      <c r="AQ5" s="24"/>
+      <c r="AR5" s="24"/>
+      <c r="AS5" s="24"/>
+      <c r="AT5" s="24"/>
+      <c r="AU5" s="24"/>
+      <c r="AV5" s="25"/>
+      <c r="AW5" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="AX5" s="38"/>
+      <c r="AY5" s="35"/>
+      <c r="AZ5" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="BA5" s="38"/>
+      <c r="BB5" s="35"/>
+      <c r="BC5" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="BD5" s="38"/>
+      <c r="BE5" s="38"/>
+      <c r="BF5" s="38"/>
+      <c r="BG5" s="35"/>
+      <c r="BH5" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="BI5" s="38"/>
+      <c r="BJ5" s="38"/>
+      <c r="BK5" s="38"/>
+      <c r="BL5" s="35"/>
+      <c r="BM5" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="BN5" s="38"/>
+      <c r="BO5" s="38"/>
+      <c r="BP5" s="38"/>
+      <c r="BQ5" s="38"/>
+      <c r="BR5" s="38"/>
+      <c r="BS5" s="38"/>
+      <c r="BT5" s="38"/>
+      <c r="BU5" s="38"/>
+      <c r="BV5" s="38"/>
+      <c r="BW5" s="38"/>
+      <c r="BX5" s="38"/>
+      <c r="BY5" s="38"/>
+      <c r="BZ5" s="38"/>
+      <c r="CA5" s="38"/>
+      <c r="CB5" s="38"/>
+      <c r="CC5" s="38"/>
+      <c r="CD5" s="38"/>
+      <c r="CE5" s="38"/>
+      <c r="CF5" s="35"/>
+    </row>
+    <row r="6" spans="2:84">
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="25"/>
+      <c r="V6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="25"/>
+      <c r="AE6" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="24"/>
+      <c r="AI6" s="24"/>
+      <c r="AJ6" s="24"/>
+      <c r="AK6" s="24"/>
+      <c r="AL6" s="24"/>
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO6" s="24"/>
+      <c r="AP6" s="24"/>
+      <c r="AQ6" s="24"/>
+      <c r="AR6" s="24"/>
+      <c r="AS6" s="24"/>
+      <c r="AT6" s="24"/>
+      <c r="AU6" s="24"/>
+      <c r="AV6" s="25"/>
+      <c r="AW6" s="36"/>
+      <c r="AX6" s="39"/>
+      <c r="AY6" s="37"/>
+      <c r="AZ6" s="36"/>
+      <c r="BA6" s="39"/>
+      <c r="BB6" s="37"/>
+      <c r="BC6" s="36"/>
+      <c r="BD6" s="39"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="39"/>
+      <c r="BG6" s="37"/>
+      <c r="BH6" s="36"/>
+      <c r="BI6" s="39"/>
+      <c r="BJ6" s="39"/>
+      <c r="BK6" s="39"/>
+      <c r="BL6" s="37"/>
+      <c r="BM6" s="36"/>
+      <c r="BN6" s="39"/>
+      <c r="BO6" s="39"/>
+      <c r="BP6" s="39"/>
+      <c r="BQ6" s="39"/>
+      <c r="BR6" s="39"/>
+      <c r="BS6" s="39"/>
+      <c r="BT6" s="39"/>
+      <c r="BU6" s="39"/>
+      <c r="BV6" s="39"/>
+      <c r="BW6" s="39"/>
+      <c r="BX6" s="39"/>
+      <c r="BY6" s="39"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="39"/>
+      <c r="CB6" s="39"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="39"/>
+      <c r="CE6" s="39"/>
+      <c r="CF6" s="37"/>
+    </row>
+    <row r="7" spans="2:84">
+      <c r="B7" s="23">
+        <v>1</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="38"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="24"/>
+      <c r="AJ7" s="24"/>
+      <c r="AK7" s="24"/>
+      <c r="AL7" s="24"/>
+      <c r="AM7" s="25"/>
+      <c r="AN7" s="23"/>
+      <c r="AO7" s="24"/>
+      <c r="AP7" s="24"/>
+      <c r="AQ7" s="24"/>
+      <c r="AR7" s="24"/>
+      <c r="AS7" s="24"/>
+      <c r="AT7" s="24"/>
+      <c r="AU7" s="24"/>
+      <c r="AV7" s="25"/>
+      <c r="AW7" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX7" s="24"/>
+      <c r="AY7" s="25"/>
+      <c r="AZ7" s="23"/>
+      <c r="BA7" s="24"/>
+      <c r="BB7" s="25"/>
+      <c r="BC7" s="23"/>
+      <c r="BD7" s="24"/>
+      <c r="BE7" s="24"/>
+      <c r="BF7" s="24"/>
+      <c r="BG7" s="25"/>
+      <c r="BH7" s="23"/>
+      <c r="BI7" s="24"/>
+      <c r="BJ7" s="24"/>
+      <c r="BK7" s="24"/>
+      <c r="BL7" s="25"/>
+      <c r="BM7" s="48"/>
+      <c r="BN7" s="49"/>
+      <c r="BO7" s="49"/>
+      <c r="BP7" s="49"/>
+      <c r="BQ7" s="49"/>
+      <c r="BR7" s="49"/>
+      <c r="BS7" s="49"/>
+      <c r="BT7" s="49"/>
+      <c r="BU7" s="49"/>
+      <c r="BV7" s="49"/>
+      <c r="BW7" s="49"/>
+      <c r="BX7" s="49"/>
+      <c r="BY7" s="49"/>
+      <c r="BZ7" s="49"/>
+      <c r="CA7" s="49"/>
+      <c r="CB7" s="49"/>
+      <c r="CC7" s="49"/>
+      <c r="CD7" s="49"/>
+      <c r="CE7" s="49"/>
+      <c r="CF7" s="50"/>
+    </row>
+    <row r="8" spans="2:84" ht="37.5" customHeight="1">
+      <c r="B8" s="23">
+        <v>2</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="37"/>
+      <c r="V8" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="24"/>
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="24"/>
+      <c r="AJ8" s="24"/>
+      <c r="AK8" s="24"/>
+      <c r="AL8" s="24"/>
+      <c r="AM8" s="25"/>
+      <c r="AN8" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO8" s="24"/>
+      <c r="AP8" s="24"/>
+      <c r="AQ8" s="24"/>
+      <c r="AR8" s="24"/>
+      <c r="AS8" s="24"/>
+      <c r="AT8" s="24"/>
+      <c r="AU8" s="24"/>
+      <c r="AV8" s="25"/>
+      <c r="AW8" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX8" s="24"/>
+      <c r="AY8" s="25"/>
+      <c r="AZ8" s="23"/>
+      <c r="BA8" s="24"/>
+      <c r="BB8" s="25"/>
+      <c r="BC8" s="23"/>
+      <c r="BD8" s="24"/>
+      <c r="BE8" s="24"/>
+      <c r="BF8" s="24"/>
+      <c r="BG8" s="25"/>
+      <c r="BH8" s="23"/>
+      <c r="BI8" s="24"/>
+      <c r="BJ8" s="24"/>
+      <c r="BK8" s="24"/>
+      <c r="BL8" s="25"/>
+      <c r="BM8" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="BN8" s="46"/>
+      <c r="BO8" s="46"/>
+      <c r="BP8" s="46"/>
+      <c r="BQ8" s="46"/>
+      <c r="BR8" s="46"/>
+      <c r="BS8" s="46"/>
+      <c r="BT8" s="46"/>
+      <c r="BU8" s="46"/>
+      <c r="BV8" s="46"/>
+      <c r="BW8" s="46"/>
+      <c r="BX8" s="46"/>
+      <c r="BY8" s="46"/>
+      <c r="BZ8" s="46"/>
+      <c r="CA8" s="46"/>
+      <c r="CB8" s="46"/>
+      <c r="CC8" s="46"/>
+      <c r="CD8" s="46"/>
+      <c r="CE8" s="46"/>
+      <c r="CF8" s="47"/>
+    </row>
+    <row r="9" spans="2:84">
+      <c r="B9" s="23">
+        <v>3</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="24"/>
+      <c r="AJ9" s="24"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="25"/>
+      <c r="AN9" s="23"/>
+      <c r="AO9" s="24"/>
+      <c r="AP9" s="24"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="24"/>
+      <c r="AS9" s="24"/>
+      <c r="AT9" s="24"/>
+      <c r="AU9" s="24"/>
+      <c r="AV9" s="25"/>
+      <c r="AW9" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX9" s="24"/>
+      <c r="AY9" s="25"/>
+      <c r="AZ9" s="23"/>
+      <c r="BA9" s="24"/>
+      <c r="BB9" s="25"/>
+      <c r="BC9" s="23"/>
+      <c r="BD9" s="24"/>
+      <c r="BE9" s="24"/>
+      <c r="BF9" s="24"/>
+      <c r="BG9" s="25"/>
+      <c r="BH9" s="23"/>
+      <c r="BI9" s="24"/>
+      <c r="BJ9" s="24"/>
+      <c r="BK9" s="24"/>
+      <c r="BL9" s="25"/>
+      <c r="BM9" s="48"/>
+      <c r="BN9" s="49"/>
+      <c r="BO9" s="49"/>
+      <c r="BP9" s="49"/>
+      <c r="BQ9" s="49"/>
+      <c r="BR9" s="49"/>
+      <c r="BS9" s="49"/>
+      <c r="BT9" s="49"/>
+      <c r="BU9" s="49"/>
+      <c r="BV9" s="49"/>
+      <c r="BW9" s="49"/>
+      <c r="BX9" s="49"/>
+      <c r="BY9" s="49"/>
+      <c r="BZ9" s="49"/>
+      <c r="CA9" s="49"/>
+      <c r="CB9" s="49"/>
+      <c r="CC9" s="49"/>
+      <c r="CD9" s="49"/>
+      <c r="CE9" s="49"/>
+      <c r="CF9" s="50"/>
+    </row>
+    <row r="10" spans="2:84">
+      <c r="B10" s="23">
+        <v>4</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="26"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="44"/>
+      <c r="V10" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="W10" s="38"/>
+      <c r="X10" s="38"/>
+      <c r="Y10" s="38"/>
+      <c r="Z10" s="38"/>
+      <c r="AA10" s="38"/>
+      <c r="AB10" s="38"/>
+      <c r="AC10" s="38"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF10" s="38"/>
+      <c r="AG10" s="38"/>
+      <c r="AH10" s="38"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="38"/>
+      <c r="AK10" s="38"/>
+      <c r="AL10" s="38"/>
+      <c r="AM10" s="35"/>
+      <c r="AN10" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="AO10" s="24"/>
+      <c r="AP10" s="24"/>
+      <c r="AQ10" s="24"/>
+      <c r="AR10" s="24"/>
+      <c r="AS10" s="24"/>
+      <c r="AT10" s="24"/>
+      <c r="AU10" s="24"/>
+      <c r="AV10" s="25"/>
+      <c r="AW10" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX10" s="24"/>
+      <c r="AY10" s="25"/>
+      <c r="AZ10" s="23"/>
+      <c r="BA10" s="24"/>
+      <c r="BB10" s="25"/>
+      <c r="BC10" s="23"/>
+      <c r="BD10" s="24"/>
+      <c r="BE10" s="24"/>
+      <c r="BF10" s="24"/>
+      <c r="BG10" s="25"/>
+      <c r="BH10" s="23"/>
+      <c r="BI10" s="24"/>
+      <c r="BJ10" s="24"/>
+      <c r="BK10" s="24"/>
+      <c r="BL10" s="25"/>
+      <c r="BM10" s="48"/>
+      <c r="BN10" s="49"/>
+      <c r="BO10" s="49"/>
+      <c r="BP10" s="49"/>
+      <c r="BQ10" s="49"/>
+      <c r="BR10" s="49"/>
+      <c r="BS10" s="49"/>
+      <c r="BT10" s="49"/>
+      <c r="BU10" s="49"/>
+      <c r="BV10" s="49"/>
+      <c r="BW10" s="49"/>
+      <c r="BX10" s="49"/>
+      <c r="BY10" s="49"/>
+      <c r="BZ10" s="49"/>
+      <c r="CA10" s="49"/>
+      <c r="CB10" s="49"/>
+      <c r="CC10" s="49"/>
+      <c r="CD10" s="49"/>
+      <c r="CE10" s="49"/>
+      <c r="CF10" s="50"/>
+    </row>
+    <row r="11" spans="2:84">
+      <c r="B11" s="23"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="31"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="44"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="44"/>
+      <c r="AE11" s="36"/>
+      <c r="AF11" s="39"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="39"/>
+      <c r="AJ11" s="39"/>
+      <c r="AK11" s="39"/>
+      <c r="AL11" s="39"/>
+      <c r="AM11" s="37"/>
+      <c r="AN11" s="23" t="s">
+        <v>71</v>
+      </c>
+      <c r="AO11" s="24"/>
+      <c r="AP11" s="24"/>
+      <c r="AQ11" s="24"/>
+      <c r="AR11" s="24"/>
+      <c r="AS11" s="24"/>
+      <c r="AT11" s="24"/>
+      <c r="AU11" s="24"/>
+      <c r="AV11" s="25"/>
+      <c r="AW11" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX11" s="24"/>
+      <c r="AY11" s="25"/>
+      <c r="AZ11" s="23"/>
+      <c r="BA11" s="24"/>
+      <c r="BB11" s="25"/>
+      <c r="BC11" s="23"/>
+      <c r="BD11" s="24"/>
+      <c r="BE11" s="24"/>
+      <c r="BF11" s="24"/>
+      <c r="BG11" s="25"/>
+      <c r="BH11" s="23"/>
+      <c r="BI11" s="24"/>
+      <c r="BJ11" s="24"/>
+      <c r="BK11" s="24"/>
+      <c r="BL11" s="25"/>
+      <c r="BM11" s="48"/>
+      <c r="BN11" s="49"/>
+      <c r="BO11" s="49"/>
+      <c r="BP11" s="49"/>
+      <c r="BQ11" s="49"/>
+      <c r="BR11" s="49"/>
+      <c r="BS11" s="49"/>
+      <c r="BT11" s="49"/>
+      <c r="BU11" s="49"/>
+      <c r="BV11" s="49"/>
+      <c r="BW11" s="49"/>
+      <c r="BX11" s="49"/>
+      <c r="BY11" s="49"/>
+      <c r="BZ11" s="49"/>
+      <c r="CA11" s="49"/>
+      <c r="CB11" s="49"/>
+      <c r="CC11" s="49"/>
+      <c r="CD11" s="49"/>
+      <c r="CE11" s="49"/>
+      <c r="CF11" s="50"/>
+    </row>
+    <row r="12" spans="2:84">
+      <c r="B12" s="23"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="26"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="31"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="31"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="44"/>
+      <c r="AE12" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
+      <c r="AH12" s="24"/>
+      <c r="AI12" s="24"/>
+      <c r="AJ12" s="24"/>
+      <c r="AK12" s="24"/>
+      <c r="AL12" s="24"/>
+      <c r="AM12" s="25"/>
+      <c r="AN12" s="23"/>
+      <c r="AO12" s="24"/>
+      <c r="AP12" s="24"/>
+      <c r="AQ12" s="24"/>
+      <c r="AR12" s="24"/>
+      <c r="AS12" s="24"/>
+      <c r="AT12" s="24"/>
+      <c r="AU12" s="24"/>
+      <c r="AV12" s="25"/>
+      <c r="AW12" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX12" s="24"/>
+      <c r="AY12" s="25"/>
+      <c r="AZ12" s="23"/>
+      <c r="BA12" s="24"/>
+      <c r="BB12" s="25"/>
+      <c r="BC12" s="23"/>
+      <c r="BD12" s="24"/>
+      <c r="BE12" s="24"/>
+      <c r="BF12" s="24"/>
+      <c r="BG12" s="25"/>
+      <c r="BH12" s="23"/>
+      <c r="BI12" s="24"/>
+      <c r="BJ12" s="24"/>
+      <c r="BK12" s="24"/>
+      <c r="BL12" s="25"/>
+      <c r="BM12" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="BN12" s="49"/>
+      <c r="BO12" s="49"/>
+      <c r="BP12" s="49"/>
+      <c r="BQ12" s="49"/>
+      <c r="BR12" s="49"/>
+      <c r="BS12" s="49"/>
+      <c r="BT12" s="49"/>
+      <c r="BU12" s="49"/>
+      <c r="BV12" s="49"/>
+      <c r="BW12" s="49"/>
+      <c r="BX12" s="49"/>
+      <c r="BY12" s="49"/>
+      <c r="BZ12" s="49"/>
+      <c r="CA12" s="49"/>
+      <c r="CB12" s="49"/>
+      <c r="CC12" s="49"/>
+      <c r="CD12" s="49"/>
+      <c r="CE12" s="49"/>
+      <c r="CF12" s="50"/>
+    </row>
+    <row r="13" spans="2:84">
+      <c r="B13" s="27"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="39"/>
+      <c r="X13" s="39"/>
+      <c r="Y13" s="39"/>
+      <c r="Z13" s="39"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="39"/>
+      <c r="AC13" s="39"/>
+      <c r="AD13" s="37"/>
+      <c r="AE13" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
+      <c r="AH13" s="24"/>
+      <c r="AI13" s="24"/>
+      <c r="AJ13" s="24"/>
+      <c r="AK13" s="24"/>
+      <c r="AL13" s="24"/>
+      <c r="AM13" s="25"/>
+      <c r="AN13" s="23"/>
+      <c r="AO13" s="24"/>
+      <c r="AP13" s="24"/>
+      <c r="AQ13" s="24"/>
+      <c r="AR13" s="24"/>
+      <c r="AS13" s="24"/>
+      <c r="AT13" s="24"/>
+      <c r="AU13" s="24"/>
+      <c r="AV13" s="25"/>
+      <c r="AW13" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX13" s="24"/>
+      <c r="AY13" s="25"/>
+      <c r="AZ13" s="23"/>
+      <c r="BA13" s="24"/>
+      <c r="BB13" s="25"/>
+      <c r="BC13" s="23"/>
+      <c r="BD13" s="24"/>
+      <c r="BE13" s="24"/>
+      <c r="BF13" s="24"/>
+      <c r="BG13" s="25"/>
+      <c r="BH13" s="23"/>
+      <c r="BI13" s="24"/>
+      <c r="BJ13" s="24"/>
+      <c r="BK13" s="24"/>
+      <c r="BL13" s="25"/>
+      <c r="BM13" s="48" t="s">
+        <v>81</v>
+      </c>
+      <c r="BN13" s="49"/>
+      <c r="BO13" s="49"/>
+      <c r="BP13" s="49"/>
+      <c r="BQ13" s="49"/>
+      <c r="BR13" s="49"/>
+      <c r="BS13" s="49"/>
+      <c r="BT13" s="49"/>
+      <c r="BU13" s="49"/>
+      <c r="BV13" s="49"/>
+      <c r="BW13" s="49"/>
+      <c r="BX13" s="49"/>
+      <c r="BY13" s="49"/>
+      <c r="BZ13" s="49"/>
+      <c r="CA13" s="49"/>
+      <c r="CB13" s="49"/>
+      <c r="CC13" s="49"/>
+      <c r="CD13" s="49"/>
+      <c r="CE13" s="49"/>
+      <c r="CF13" s="50"/>
+    </row>
+    <row r="14" spans="2:84">
+      <c r="B14" s="23">
+        <v>5</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="31"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="31"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="38"/>
+      <c r="X14" s="38"/>
+      <c r="Y14" s="38"/>
+      <c r="Z14" s="38"/>
+      <c r="AA14" s="38"/>
+      <c r="AB14" s="38"/>
+      <c r="AC14" s="38"/>
+      <c r="AD14" s="35"/>
+      <c r="AE14" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
+      <c r="AH14" s="24"/>
+      <c r="AI14" s="24"/>
+      <c r="AJ14" s="24"/>
+      <c r="AK14" s="24"/>
+      <c r="AL14" s="24"/>
+      <c r="AM14" s="25"/>
+      <c r="AN14" s="23"/>
+      <c r="AO14" s="24"/>
+      <c r="AP14" s="24"/>
+      <c r="AQ14" s="24"/>
+      <c r="AR14" s="24"/>
+      <c r="AS14" s="24"/>
+      <c r="AT14" s="24"/>
+      <c r="AU14" s="24"/>
+      <c r="AV14" s="25"/>
+      <c r="AW14" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX14" s="24"/>
+      <c r="AY14" s="25"/>
+      <c r="AZ14" s="23"/>
+      <c r="BA14" s="24"/>
+      <c r="BB14" s="25"/>
+      <c r="BC14" s="23"/>
+      <c r="BD14" s="24"/>
+      <c r="BE14" s="24"/>
+      <c r="BF14" s="24"/>
+      <c r="BG14" s="25"/>
+      <c r="BH14" s="23"/>
+      <c r="BI14" s="24"/>
+      <c r="BJ14" s="24"/>
+      <c r="BK14" s="24"/>
+      <c r="BL14" s="25"/>
+      <c r="BM14" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="BN14" s="52"/>
+      <c r="BO14" s="52"/>
+      <c r="BP14" s="52"/>
+      <c r="BQ14" s="52"/>
+      <c r="BR14" s="52"/>
+      <c r="BS14" s="52"/>
+      <c r="BT14" s="52"/>
+      <c r="BU14" s="52"/>
+      <c r="BV14" s="52"/>
+      <c r="BW14" s="52"/>
+      <c r="BX14" s="52"/>
+      <c r="BY14" s="52"/>
+      <c r="BZ14" s="52"/>
+      <c r="CA14" s="52"/>
+      <c r="CB14" s="52"/>
+      <c r="CC14" s="52"/>
+      <c r="CD14" s="52"/>
+      <c r="CE14" s="52"/>
+      <c r="CF14" s="53"/>
+    </row>
+    <row r="15" spans="2:84">
+      <c r="B15" s="23"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="36"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="39"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39"/>
+      <c r="S15" s="39"/>
+      <c r="T15" s="39"/>
+      <c r="U15" s="37"/>
+      <c r="V15" s="36"/>
+      <c r="W15" s="39"/>
+      <c r="X15" s="39"/>
+      <c r="Y15" s="39"/>
+      <c r="Z15" s="39"/>
+      <c r="AA15" s="39"/>
+      <c r="AB15" s="39"/>
+      <c r="AC15" s="39"/>
+      <c r="AD15" s="37"/>
+      <c r="AE15" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
+      <c r="AH15" s="24"/>
+      <c r="AI15" s="24"/>
+      <c r="AJ15" s="24"/>
+      <c r="AK15" s="24"/>
+      <c r="AL15" s="24"/>
+      <c r="AM15" s="25"/>
+      <c r="AN15" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="AO15" s="24"/>
+      <c r="AP15" s="24"/>
+      <c r="AQ15" s="24"/>
+      <c r="AR15" s="24"/>
+      <c r="AS15" s="24"/>
+      <c r="AT15" s="24"/>
+      <c r="AU15" s="24"/>
+      <c r="AV15" s="25"/>
+      <c r="AW15" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX15" s="24"/>
+      <c r="AY15" s="25"/>
+      <c r="AZ15" s="23"/>
+      <c r="BA15" s="24"/>
+      <c r="BB15" s="25"/>
+      <c r="BC15" s="23"/>
+      <c r="BD15" s="24"/>
+      <c r="BE15" s="24"/>
+      <c r="BF15" s="24"/>
+      <c r="BG15" s="25"/>
+      <c r="BH15" s="23"/>
+      <c r="BI15" s="24"/>
+      <c r="BJ15" s="24"/>
+      <c r="BK15" s="24"/>
+      <c r="BL15" s="25"/>
+      <c r="BM15" s="54"/>
+      <c r="BN15" s="55"/>
+      <c r="BO15" s="55"/>
+      <c r="BP15" s="55"/>
+      <c r="BQ15" s="55"/>
+      <c r="BR15" s="55"/>
+      <c r="BS15" s="55"/>
+      <c r="BT15" s="55"/>
+      <c r="BU15" s="55"/>
+      <c r="BV15" s="55"/>
+      <c r="BW15" s="55"/>
+      <c r="BX15" s="55"/>
+      <c r="BY15" s="55"/>
+      <c r="BZ15" s="55"/>
+      <c r="CA15" s="55"/>
+      <c r="CB15" s="55"/>
+      <c r="CC15" s="55"/>
+      <c r="CD15" s="55"/>
+      <c r="CE15" s="55"/>
+      <c r="CF15" s="56"/>
+    </row>
+    <row r="16" spans="2:84">
+      <c r="B16" s="23">
+        <v>6</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="34" t="s">
+        <v>91</v>
+      </c>
+      <c r="N16" s="38"/>
+      <c r="O16" s="38"/>
+      <c r="P16" s="38"/>
+      <c r="Q16" s="38"/>
+      <c r="R16" s="38"/>
+      <c r="S16" s="38"/>
+      <c r="T16" s="38"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="23" t="s">
+        <v>92</v>
+      </c>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
+      <c r="AH16" s="24"/>
+      <c r="AI16" s="24"/>
+      <c r="AJ16" s="24"/>
+      <c r="AK16" s="24"/>
+      <c r="AL16" s="24"/>
+      <c r="AM16" s="25"/>
+      <c r="AN16" s="23"/>
+      <c r="AO16" s="24"/>
+      <c r="AP16" s="24"/>
+      <c r="AQ16" s="24"/>
+      <c r="AR16" s="24"/>
+      <c r="AS16" s="24"/>
+      <c r="AT16" s="24"/>
+      <c r="AU16" s="24"/>
+      <c r="AV16" s="25"/>
+      <c r="AW16" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX16" s="24"/>
+      <c r="AY16" s="25"/>
+      <c r="AZ16" s="23"/>
+      <c r="BA16" s="24"/>
+      <c r="BB16" s="25"/>
+      <c r="BC16" s="23"/>
+      <c r="BD16" s="24"/>
+      <c r="BE16" s="24"/>
+      <c r="BF16" s="24"/>
+      <c r="BG16" s="25"/>
+      <c r="BH16" s="23"/>
+      <c r="BI16" s="24"/>
+      <c r="BJ16" s="24"/>
+      <c r="BK16" s="24"/>
+      <c r="BL16" s="25"/>
+      <c r="BM16" s="48"/>
+      <c r="BN16" s="49"/>
+      <c r="BO16" s="49"/>
+      <c r="BP16" s="49"/>
+      <c r="BQ16" s="49"/>
+      <c r="BR16" s="49"/>
+      <c r="BS16" s="49"/>
+      <c r="BT16" s="49"/>
+      <c r="BU16" s="49"/>
+      <c r="BV16" s="49"/>
+      <c r="BW16" s="49"/>
+      <c r="BX16" s="49"/>
+      <c r="BY16" s="49"/>
+      <c r="BZ16" s="49"/>
+      <c r="CA16" s="49"/>
+      <c r="CB16" s="49"/>
+      <c r="CC16" s="49"/>
+      <c r="CD16" s="49"/>
+      <c r="CE16" s="49"/>
+      <c r="CF16" s="50"/>
+    </row>
+    <row r="17" spans="2:84">
+      <c r="B17" s="23">
+        <v>7</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="W17" s="38"/>
+      <c r="X17" s="38"/>
+      <c r="Y17" s="38"/>
+      <c r="Z17" s="38"/>
+      <c r="AA17" s="38"/>
+      <c r="AB17" s="38"/>
+      <c r="AC17" s="38"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
+      <c r="AH17" s="24"/>
+      <c r="AI17" s="24"/>
+      <c r="AJ17" s="24"/>
+      <c r="AK17" s="24"/>
+      <c r="AL17" s="24"/>
+      <c r="AM17" s="25"/>
+      <c r="AN17" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="AO17" s="24"/>
+      <c r="AP17" s="24"/>
+      <c r="AQ17" s="24"/>
+      <c r="AR17" s="24"/>
+      <c r="AS17" s="24"/>
+      <c r="AT17" s="24"/>
+      <c r="AU17" s="24"/>
+      <c r="AV17" s="25"/>
+      <c r="AW17" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX17" s="24"/>
+      <c r="AY17" s="25"/>
+      <c r="AZ17" s="23"/>
+      <c r="BA17" s="24"/>
+      <c r="BB17" s="25"/>
+      <c r="BC17" s="23"/>
+      <c r="BD17" s="24"/>
+      <c r="BE17" s="24"/>
+      <c r="BF17" s="24"/>
+      <c r="BG17" s="25"/>
+      <c r="BH17" s="23"/>
+      <c r="BI17" s="24"/>
+      <c r="BJ17" s="24"/>
+      <c r="BK17" s="24"/>
+      <c r="BL17" s="25"/>
+      <c r="BM17" s="48" t="s">
+        <v>88</v>
+      </c>
+      <c r="BN17" s="49"/>
+      <c r="BO17" s="49"/>
+      <c r="BP17" s="49"/>
+      <c r="BQ17" s="49"/>
+      <c r="BR17" s="49"/>
+      <c r="BS17" s="49"/>
+      <c r="BT17" s="49"/>
+      <c r="BU17" s="49"/>
+      <c r="BV17" s="49"/>
+      <c r="BW17" s="49"/>
+      <c r="BX17" s="49"/>
+      <c r="BY17" s="49"/>
+      <c r="BZ17" s="49"/>
+      <c r="CA17" s="49"/>
+      <c r="CB17" s="49"/>
+      <c r="CC17" s="49"/>
+      <c r="CD17" s="49"/>
+      <c r="CE17" s="49"/>
+      <c r="CF17" s="50"/>
+    </row>
+    <row r="18" spans="2:84">
+      <c r="B18" s="23"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="31"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="31"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="44"/>
+      <c r="AE18" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="AF18" s="38"/>
+      <c r="AG18" s="38"/>
+      <c r="AH18" s="38"/>
+      <c r="AI18" s="38"/>
+      <c r="AJ18" s="38"/>
+      <c r="AK18" s="38"/>
+      <c r="AL18" s="38"/>
+      <c r="AM18" s="35"/>
+      <c r="AN18" s="23" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO18" s="24"/>
+      <c r="AP18" s="24"/>
+      <c r="AQ18" s="24"/>
+      <c r="AR18" s="24"/>
+      <c r="AS18" s="24"/>
+      <c r="AT18" s="24"/>
+      <c r="AU18" s="24"/>
+      <c r="AV18" s="25"/>
+      <c r="AW18" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX18" s="24"/>
+      <c r="AY18" s="25"/>
+      <c r="AZ18" s="23"/>
+      <c r="BA18" s="24"/>
+      <c r="BB18" s="25"/>
+      <c r="BC18" s="23"/>
+      <c r="BD18" s="24"/>
+      <c r="BE18" s="24"/>
+      <c r="BF18" s="24"/>
+      <c r="BG18" s="25"/>
+      <c r="BH18" s="23"/>
+      <c r="BI18" s="24"/>
+      <c r="BJ18" s="24"/>
+      <c r="BK18" s="24"/>
+      <c r="BL18" s="25"/>
+      <c r="BM18" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="BN18" s="52"/>
+      <c r="BO18" s="52"/>
+      <c r="BP18" s="52"/>
+      <c r="BQ18" s="52"/>
+      <c r="BR18" s="52"/>
+      <c r="BS18" s="52"/>
+      <c r="BT18" s="52"/>
+      <c r="BU18" s="52"/>
+      <c r="BV18" s="52"/>
+      <c r="BW18" s="52"/>
+      <c r="BX18" s="52"/>
+      <c r="BY18" s="52"/>
+      <c r="BZ18" s="52"/>
+      <c r="CA18" s="52"/>
+      <c r="CB18" s="52"/>
+      <c r="CC18" s="52"/>
+      <c r="CD18" s="52"/>
+      <c r="CE18" s="52"/>
+      <c r="CF18" s="53"/>
+    </row>
+    <row r="19" spans="2:84">
+      <c r="B19" s="23"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="26"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="31"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="31"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="44"/>
+      <c r="AE19" s="26"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="31"/>
+      <c r="AK19" s="31"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="44"/>
+      <c r="AN19" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO19" s="24"/>
+      <c r="AP19" s="24"/>
+      <c r="AQ19" s="24"/>
+      <c r="AR19" s="24"/>
+      <c r="AS19" s="24"/>
+      <c r="AT19" s="24"/>
+      <c r="AU19" s="24"/>
+      <c r="AV19" s="25"/>
+      <c r="AW19" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX19" s="24"/>
+      <c r="AY19" s="25"/>
+      <c r="AZ19" s="23"/>
+      <c r="BA19" s="24"/>
+      <c r="BB19" s="25"/>
+      <c r="BC19" s="23"/>
+      <c r="BD19" s="24"/>
+      <c r="BE19" s="24"/>
+      <c r="BF19" s="24"/>
+      <c r="BG19" s="25"/>
+      <c r="BH19" s="23"/>
+      <c r="BI19" s="24"/>
+      <c r="BJ19" s="24"/>
+      <c r="BK19" s="24"/>
+      <c r="BL19" s="25"/>
+      <c r="BM19" s="57"/>
+      <c r="BN19" s="58"/>
+      <c r="BO19" s="58"/>
+      <c r="BP19" s="58"/>
+      <c r="BQ19" s="58"/>
+      <c r="BR19" s="58"/>
+      <c r="BS19" s="58"/>
+      <c r="BT19" s="58"/>
+      <c r="BU19" s="58"/>
+      <c r="BV19" s="58"/>
+      <c r="BW19" s="58"/>
+      <c r="BX19" s="58"/>
+      <c r="BY19" s="58"/>
+      <c r="BZ19" s="58"/>
+      <c r="CA19" s="58"/>
+      <c r="CB19" s="58"/>
+      <c r="CC19" s="58"/>
+      <c r="CD19" s="58"/>
+      <c r="CE19" s="58"/>
+      <c r="CF19" s="59"/>
+    </row>
+    <row r="20" spans="2:84">
+      <c r="B20" s="23"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="44"/>
+      <c r="V20" s="36"/>
+      <c r="W20" s="39"/>
+      <c r="X20" s="39"/>
+      <c r="Y20" s="39"/>
+      <c r="Z20" s="39"/>
+      <c r="AA20" s="39"/>
+      <c r="AB20" s="39"/>
+      <c r="AC20" s="39"/>
+      <c r="AD20" s="37"/>
+      <c r="AE20" s="36"/>
+      <c r="AF20" s="39"/>
+      <c r="AG20" s="39"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="39"/>
+      <c r="AJ20" s="39"/>
+      <c r="AK20" s="39"/>
+      <c r="AL20" s="39"/>
+      <c r="AM20" s="37"/>
+      <c r="AN20" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO20" s="24"/>
+      <c r="AP20" s="24"/>
+      <c r="AQ20" s="24"/>
+      <c r="AR20" s="24"/>
+      <c r="AS20" s="24"/>
+      <c r="AT20" s="24"/>
+      <c r="AU20" s="24"/>
+      <c r="AV20" s="25"/>
+      <c r="AW20" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX20" s="24"/>
+      <c r="AY20" s="25"/>
+      <c r="AZ20" s="23"/>
+      <c r="BA20" s="24"/>
+      <c r="BB20" s="25"/>
+      <c r="BC20" s="23"/>
+      <c r="BD20" s="24"/>
+      <c r="BE20" s="24"/>
+      <c r="BF20" s="24"/>
+      <c r="BG20" s="25"/>
+      <c r="BH20" s="23"/>
+      <c r="BI20" s="24"/>
+      <c r="BJ20" s="24"/>
+      <c r="BK20" s="24"/>
+      <c r="BL20" s="25"/>
+      <c r="BM20" s="54"/>
+      <c r="BN20" s="55"/>
+      <c r="BO20" s="55"/>
+      <c r="BP20" s="55"/>
+      <c r="BQ20" s="55"/>
+      <c r="BR20" s="55"/>
+      <c r="BS20" s="55"/>
+      <c r="BT20" s="55"/>
+      <c r="BU20" s="55"/>
+      <c r="BV20" s="55"/>
+      <c r="BW20" s="55"/>
+      <c r="BX20" s="55"/>
+      <c r="BY20" s="55"/>
+      <c r="BZ20" s="55"/>
+      <c r="CA20" s="55"/>
+      <c r="CB20" s="55"/>
+      <c r="CC20" s="55"/>
+      <c r="CD20" s="55"/>
+      <c r="CE20" s="55"/>
+      <c r="CF20" s="56"/>
+    </row>
+    <row r="21" spans="2:84" ht="37.5" customHeight="1">
+      <c r="B21" s="23">
+        <v>8</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="39"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="W21" s="24"/>
+      <c r="X21" s="24"/>
+      <c r="Y21" s="24"/>
+      <c r="Z21" s="24"/>
+      <c r="AA21" s="24"/>
+      <c r="AB21" s="24"/>
+      <c r="AC21" s="24"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="23"/>
+      <c r="AF21" s="24"/>
+      <c r="AG21" s="24"/>
+      <c r="AH21" s="24"/>
+      <c r="AI21" s="24"/>
+      <c r="AJ21" s="24"/>
+      <c r="AK21" s="24"/>
+      <c r="AL21" s="24"/>
+      <c r="AM21" s="25"/>
+      <c r="AN21" s="23"/>
+      <c r="AO21" s="24"/>
+      <c r="AP21" s="24"/>
+      <c r="AQ21" s="24"/>
+      <c r="AR21" s="24"/>
+      <c r="AS21" s="24"/>
+      <c r="AT21" s="24"/>
+      <c r="AU21" s="24"/>
+      <c r="AV21" s="25"/>
+      <c r="AW21" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX21" s="24"/>
+      <c r="AY21" s="25"/>
+      <c r="AZ21" s="23"/>
+      <c r="BA21" s="24"/>
+      <c r="BB21" s="25"/>
+      <c r="BC21" s="23"/>
+      <c r="BD21" s="24"/>
+      <c r="BE21" s="24"/>
+      <c r="BF21" s="24"/>
+      <c r="BG21" s="25"/>
+      <c r="BH21" s="23"/>
+      <c r="BI21" s="24"/>
+      <c r="BJ21" s="24"/>
+      <c r="BK21" s="24"/>
+      <c r="BL21" s="25"/>
+      <c r="BM21" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="BN21" s="49"/>
+      <c r="BO21" s="49"/>
+      <c r="BP21" s="49"/>
+      <c r="BQ21" s="49"/>
+      <c r="BR21" s="49"/>
+      <c r="BS21" s="49"/>
+      <c r="BT21" s="49"/>
+      <c r="BU21" s="49"/>
+      <c r="BV21" s="49"/>
+      <c r="BW21" s="49"/>
+      <c r="BX21" s="49"/>
+      <c r="BY21" s="49"/>
+      <c r="BZ21" s="49"/>
+      <c r="CA21" s="49"/>
+      <c r="CB21" s="49"/>
+      <c r="CC21" s="49"/>
+      <c r="CD21" s="49"/>
+      <c r="CE21" s="49"/>
+      <c r="CF21" s="50"/>
+    </row>
+    <row r="22" spans="2:84">
+      <c r="B22" s="23"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="23"/>
+      <c r="AF22" s="24"/>
+      <c r="AG22" s="24"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="24"/>
+      <c r="AJ22" s="24"/>
+      <c r="AK22" s="24"/>
+      <c r="AL22" s="24"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="23"/>
+      <c r="AO22" s="24"/>
+      <c r="AP22" s="24"/>
+      <c r="AQ22" s="24"/>
+      <c r="AR22" s="24"/>
+      <c r="AS22" s="24"/>
+      <c r="AT22" s="24"/>
+      <c r="AU22" s="24"/>
+      <c r="AV22" s="25"/>
+      <c r="AW22" s="23"/>
+      <c r="AX22" s="24"/>
+      <c r="AY22" s="25"/>
+      <c r="AZ22" s="23"/>
+      <c r="BA22" s="24"/>
+      <c r="BB22" s="25"/>
+      <c r="BC22" s="23"/>
+      <c r="BD22" s="24"/>
+      <c r="BE22" s="24"/>
+      <c r="BF22" s="24"/>
+      <c r="BG22" s="25"/>
+      <c r="BH22" s="23"/>
+      <c r="BI22" s="24"/>
+      <c r="BJ22" s="24"/>
+      <c r="BK22" s="24"/>
+      <c r="BL22" s="25"/>
+      <c r="BM22" s="48"/>
+      <c r="BN22" s="49"/>
+      <c r="BO22" s="49"/>
+      <c r="BP22" s="49"/>
+      <c r="BQ22" s="49"/>
+      <c r="BR22" s="49"/>
+      <c r="BS22" s="49"/>
+      <c r="BT22" s="49"/>
+      <c r="BU22" s="49"/>
+      <c r="BV22" s="49"/>
+      <c r="BW22" s="49"/>
+      <c r="BX22" s="49"/>
+      <c r="BY22" s="49"/>
+      <c r="BZ22" s="49"/>
+      <c r="CA22" s="49"/>
+      <c r="CB22" s="49"/>
+      <c r="CC22" s="49"/>
+      <c r="CD22" s="49"/>
+      <c r="CE22" s="49"/>
+      <c r="CF22" s="50"/>
+    </row>
+    <row r="23" spans="2:84">
+      <c r="B23" s="23"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="24"/>
+      <c r="AG23" s="24"/>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="24"/>
+      <c r="AJ23" s="24"/>
+      <c r="AK23" s="24"/>
+      <c r="AL23" s="24"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="23"/>
+      <c r="AO23" s="24"/>
+      <c r="AP23" s="24"/>
+      <c r="AQ23" s="24"/>
+      <c r="AR23" s="24"/>
+      <c r="AS23" s="24"/>
+      <c r="AT23" s="24"/>
+      <c r="AU23" s="24"/>
+      <c r="AV23" s="25"/>
+      <c r="AW23" s="23"/>
+      <c r="AX23" s="24"/>
+      <c r="AY23" s="25"/>
+      <c r="AZ23" s="23"/>
+      <c r="BA23" s="24"/>
+      <c r="BB23" s="25"/>
+      <c r="BC23" s="23"/>
+      <c r="BD23" s="24"/>
+      <c r="BE23" s="24"/>
+      <c r="BF23" s="24"/>
+      <c r="BG23" s="25"/>
+      <c r="BH23" s="23"/>
+      <c r="BI23" s="24"/>
+      <c r="BJ23" s="24"/>
+      <c r="BK23" s="24"/>
+      <c r="BL23" s="25"/>
+      <c r="BM23" s="48"/>
+      <c r="BN23" s="49"/>
+      <c r="BO23" s="49"/>
+      <c r="BP23" s="49"/>
+      <c r="BQ23" s="49"/>
+      <c r="BR23" s="49"/>
+      <c r="BS23" s="49"/>
+      <c r="BT23" s="49"/>
+      <c r="BU23" s="49"/>
+      <c r="BV23" s="49"/>
+      <c r="BW23" s="49"/>
+      <c r="BX23" s="49"/>
+      <c r="BY23" s="49"/>
+      <c r="BZ23" s="49"/>
+      <c r="CA23" s="49"/>
+      <c r="CB23" s="49"/>
+      <c r="CC23" s="49"/>
+      <c r="CD23" s="49"/>
+      <c r="CE23" s="49"/>
+      <c r="CF23" s="50"/>
+    </row>
+    <row r="24" spans="2:84">
+      <c r="B24" s="23"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="24"/>
+      <c r="T24" s="24"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="24"/>
+      <c r="X24" s="24"/>
+      <c r="Y24" s="24"/>
+      <c r="Z24" s="24"/>
+      <c r="AA24" s="24"/>
+      <c r="AB24" s="24"/>
+      <c r="AC24" s="24"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="23"/>
+      <c r="AF24" s="24"/>
+      <c r="AG24" s="24"/>
+      <c r="AH24" s="24"/>
+      <c r="AI24" s="24"/>
+      <c r="AJ24" s="24"/>
+      <c r="AK24" s="24"/>
+      <c r="AL24" s="24"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="23"/>
+      <c r="AO24" s="24"/>
+      <c r="AP24" s="24"/>
+      <c r="AQ24" s="24"/>
+      <c r="AR24" s="24"/>
+      <c r="AS24" s="24"/>
+      <c r="AT24" s="24"/>
+      <c r="AU24" s="24"/>
+      <c r="AV24" s="25"/>
+      <c r="AW24" s="23"/>
+      <c r="AX24" s="24"/>
+      <c r="AY24" s="25"/>
+      <c r="AZ24" s="23"/>
+      <c r="BA24" s="24"/>
+      <c r="BB24" s="25"/>
+      <c r="BC24" s="23"/>
+      <c r="BD24" s="24"/>
+      <c r="BE24" s="24"/>
+      <c r="BF24" s="24"/>
+      <c r="BG24" s="25"/>
+      <c r="BH24" s="23"/>
+      <c r="BI24" s="24"/>
+      <c r="BJ24" s="24"/>
+      <c r="BK24" s="24"/>
+      <c r="BL24" s="25"/>
+      <c r="BM24" s="48"/>
+      <c r="BN24" s="49"/>
+      <c r="BO24" s="49"/>
+      <c r="BP24" s="49"/>
+      <c r="BQ24" s="49"/>
+      <c r="BR24" s="49"/>
+      <c r="BS24" s="49"/>
+      <c r="BT24" s="49"/>
+      <c r="BU24" s="49"/>
+      <c r="BV24" s="49"/>
+      <c r="BW24" s="49"/>
+      <c r="BX24" s="49"/>
+      <c r="BY24" s="49"/>
+      <c r="BZ24" s="49"/>
+      <c r="CA24" s="49"/>
+      <c r="CB24" s="49"/>
+      <c r="CC24" s="49"/>
+      <c r="CD24" s="49"/>
+      <c r="CE24" s="49"/>
+      <c r="CF24" s="50"/>
+    </row>
+    <row r="25" spans="2:84">
+      <c r="B25" s="23"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="23"/>
+      <c r="AF25" s="24"/>
+      <c r="AG25" s="24"/>
+      <c r="AH25" s="24"/>
+      <c r="AI25" s="24"/>
+      <c r="AJ25" s="24"/>
+      <c r="AK25" s="24"/>
+      <c r="AL25" s="24"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="23"/>
+      <c r="AO25" s="24"/>
+      <c r="AP25" s="24"/>
+      <c r="AQ25" s="24"/>
+      <c r="AR25" s="24"/>
+      <c r="AS25" s="24"/>
+      <c r="AT25" s="24"/>
+      <c r="AU25" s="24"/>
+      <c r="AV25" s="25"/>
+      <c r="AW25" s="23"/>
+      <c r="AX25" s="24"/>
+      <c r="AY25" s="25"/>
+      <c r="AZ25" s="23"/>
+      <c r="BA25" s="24"/>
+      <c r="BB25" s="25"/>
+      <c r="BC25" s="23"/>
+      <c r="BD25" s="24"/>
+      <c r="BE25" s="24"/>
+      <c r="BF25" s="24"/>
+      <c r="BG25" s="25"/>
+      <c r="BH25" s="23"/>
+      <c r="BI25" s="24"/>
+      <c r="BJ25" s="24"/>
+      <c r="BK25" s="24"/>
+      <c r="BL25" s="25"/>
+      <c r="BM25" s="48"/>
+      <c r="BN25" s="49"/>
+      <c r="BO25" s="49"/>
+      <c r="BP25" s="49"/>
+      <c r="BQ25" s="49"/>
+      <c r="BR25" s="49"/>
+      <c r="BS25" s="49"/>
+      <c r="BT25" s="49"/>
+      <c r="BU25" s="49"/>
+      <c r="BV25" s="49"/>
+      <c r="BW25" s="49"/>
+      <c r="BX25" s="49"/>
+      <c r="BY25" s="49"/>
+      <c r="BZ25" s="49"/>
+      <c r="CA25" s="49"/>
+      <c r="CB25" s="49"/>
+      <c r="CC25" s="49"/>
+      <c r="CD25" s="49"/>
+      <c r="CE25" s="49"/>
+      <c r="CF25" s="50"/>
+    </row>
+    <row r="26" spans="2:84">
+      <c r="B26" s="23"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="24"/>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="24"/>
+      <c r="AB26" s="24"/>
+      <c r="AC26" s="24"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="23"/>
+      <c r="AF26" s="24"/>
+      <c r="AG26" s="24"/>
+      <c r="AH26" s="24"/>
+      <c r="AI26" s="24"/>
+      <c r="AJ26" s="24"/>
+      <c r="AK26" s="24"/>
+      <c r="AL26" s="24"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="23"/>
+      <c r="AO26" s="24"/>
+      <c r="AP26" s="24"/>
+      <c r="AQ26" s="24"/>
+      <c r="AR26" s="24"/>
+      <c r="AS26" s="24"/>
+      <c r="AT26" s="24"/>
+      <c r="AU26" s="24"/>
+      <c r="AV26" s="25"/>
+      <c r="AW26" s="23"/>
+      <c r="AX26" s="24"/>
+      <c r="AY26" s="25"/>
+      <c r="AZ26" s="23"/>
+      <c r="BA26" s="24"/>
+      <c r="BB26" s="25"/>
+      <c r="BC26" s="23"/>
+      <c r="BD26" s="24"/>
+      <c r="BE26" s="24"/>
+      <c r="BF26" s="24"/>
+      <c r="BG26" s="25"/>
+      <c r="BH26" s="23"/>
+      <c r="BI26" s="24"/>
+      <c r="BJ26" s="24"/>
+      <c r="BK26" s="24"/>
+      <c r="BL26" s="25"/>
+      <c r="BM26" s="48"/>
+      <c r="BN26" s="49"/>
+      <c r="BO26" s="49"/>
+      <c r="BP26" s="49"/>
+      <c r="BQ26" s="49"/>
+      <c r="BR26" s="49"/>
+      <c r="BS26" s="49"/>
+      <c r="BT26" s="49"/>
+      <c r="BU26" s="49"/>
+      <c r="BV26" s="49"/>
+      <c r="BW26" s="49"/>
+      <c r="BX26" s="49"/>
+      <c r="BY26" s="49"/>
+      <c r="BZ26" s="49"/>
+      <c r="CA26" s="49"/>
+      <c r="CB26" s="49"/>
+      <c r="CC26" s="49"/>
+      <c r="CD26" s="49"/>
+      <c r="CE26" s="49"/>
+      <c r="CF26" s="50"/>
+    </row>
+    <row r="27" spans="2:84">
+      <c r="B27" s="23"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="23"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="23"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="24"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="23"/>
+      <c r="AF27" s="24"/>
+      <c r="AG27" s="24"/>
+      <c r="AH27" s="24"/>
+      <c r="AI27" s="24"/>
+      <c r="AJ27" s="24"/>
+      <c r="AK27" s="24"/>
+      <c r="AL27" s="24"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="23"/>
+      <c r="AO27" s="24"/>
+      <c r="AP27" s="24"/>
+      <c r="AQ27" s="24"/>
+      <c r="AR27" s="24"/>
+      <c r="AS27" s="24"/>
+      <c r="AT27" s="24"/>
+      <c r="AU27" s="24"/>
+      <c r="AV27" s="25"/>
+      <c r="AW27" s="23"/>
+      <c r="AX27" s="24"/>
+      <c r="AY27" s="25"/>
+      <c r="AZ27" s="23"/>
+      <c r="BA27" s="24"/>
+      <c r="BB27" s="25"/>
+      <c r="BC27" s="23"/>
+      <c r="BD27" s="24"/>
+      <c r="BE27" s="24"/>
+      <c r="BF27" s="24"/>
+      <c r="BG27" s="25"/>
+      <c r="BH27" s="23"/>
+      <c r="BI27" s="24"/>
+      <c r="BJ27" s="24"/>
+      <c r="BK27" s="24"/>
+      <c r="BL27" s="25"/>
+      <c r="BM27" s="48"/>
+      <c r="BN27" s="49"/>
+      <c r="BO27" s="49"/>
+      <c r="BP27" s="49"/>
+      <c r="BQ27" s="49"/>
+      <c r="BR27" s="49"/>
+      <c r="BS27" s="49"/>
+      <c r="BT27" s="49"/>
+      <c r="BU27" s="49"/>
+      <c r="BV27" s="49"/>
+      <c r="BW27" s="49"/>
+      <c r="BX27" s="49"/>
+      <c r="BY27" s="49"/>
+      <c r="BZ27" s="49"/>
+      <c r="CA27" s="49"/>
+      <c r="CB27" s="49"/>
+      <c r="CC27" s="49"/>
+      <c r="CD27" s="49"/>
+      <c r="CE27" s="49"/>
+      <c r="CF27" s="50"/>
+    </row>
+    <row r="28" spans="2:84">
+      <c r="B28" s="23"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="23"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="23"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="24"/>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
+      <c r="AB28" s="24"/>
+      <c r="AC28" s="24"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="23"/>
+      <c r="AF28" s="24"/>
+      <c r="AG28" s="24"/>
+      <c r="AH28" s="24"/>
+      <c r="AI28" s="24"/>
+      <c r="AJ28" s="24"/>
+      <c r="AK28" s="24"/>
+      <c r="AL28" s="24"/>
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="23"/>
+      <c r="AO28" s="24"/>
+      <c r="AP28" s="24"/>
+      <c r="AQ28" s="24"/>
+      <c r="AR28" s="24"/>
+      <c r="AS28" s="24"/>
+      <c r="AT28" s="24"/>
+      <c r="AU28" s="24"/>
+      <c r="AV28" s="25"/>
+      <c r="AW28" s="23"/>
+      <c r="AX28" s="24"/>
+      <c r="AY28" s="25"/>
+      <c r="AZ28" s="23"/>
+      <c r="BA28" s="24"/>
+      <c r="BB28" s="25"/>
+      <c r="BC28" s="23"/>
+      <c r="BD28" s="24"/>
+      <c r="BE28" s="24"/>
+      <c r="BF28" s="24"/>
+      <c r="BG28" s="25"/>
+      <c r="BH28" s="23"/>
+      <c r="BI28" s="24"/>
+      <c r="BJ28" s="24"/>
+      <c r="BK28" s="24"/>
+      <c r="BL28" s="25"/>
+      <c r="BM28" s="48"/>
+      <c r="BN28" s="49"/>
+      <c r="BO28" s="49"/>
+      <c r="BP28" s="49"/>
+      <c r="BQ28" s="49"/>
+      <c r="BR28" s="49"/>
+      <c r="BS28" s="49"/>
+      <c r="BT28" s="49"/>
+      <c r="BU28" s="49"/>
+      <c r="BV28" s="49"/>
+      <c r="BW28" s="49"/>
+      <c r="BX28" s="49"/>
+      <c r="BY28" s="49"/>
+      <c r="BZ28" s="49"/>
+      <c r="CA28" s="49"/>
+      <c r="CB28" s="49"/>
+      <c r="CC28" s="49"/>
+      <c r="CD28" s="49"/>
+      <c r="CE28" s="49"/>
+      <c r="CF28" s="50"/>
+    </row>
+    <row r="29" spans="2:84">
+      <c r="B29" s="23"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="23"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="23"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="24"/>
+      <c r="AB29" s="24"/>
+      <c r="AC29" s="24"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="23"/>
+      <c r="AF29" s="24"/>
+      <c r="AG29" s="24"/>
+      <c r="AH29" s="24"/>
+      <c r="AI29" s="24"/>
+      <c r="AJ29" s="24"/>
+      <c r="AK29" s="24"/>
+      <c r="AL29" s="24"/>
+      <c r="AM29" s="25"/>
+      <c r="AN29" s="23"/>
+      <c r="AO29" s="24"/>
+      <c r="AP29" s="24"/>
+      <c r="AQ29" s="24"/>
+      <c r="AR29" s="24"/>
+      <c r="AS29" s="24"/>
+      <c r="AT29" s="24"/>
+      <c r="AU29" s="24"/>
+      <c r="AV29" s="25"/>
+      <c r="AW29" s="23"/>
+      <c r="AX29" s="24"/>
+      <c r="AY29" s="25"/>
+      <c r="AZ29" s="23"/>
+      <c r="BA29" s="24"/>
+      <c r="BB29" s="25"/>
+      <c r="BC29" s="23"/>
+      <c r="BD29" s="24"/>
+      <c r="BE29" s="24"/>
+      <c r="BF29" s="24"/>
+      <c r="BG29" s="25"/>
+      <c r="BH29" s="23"/>
+      <c r="BI29" s="24"/>
+      <c r="BJ29" s="24"/>
+      <c r="BK29" s="24"/>
+      <c r="BL29" s="25"/>
+      <c r="BM29" s="48"/>
+      <c r="BN29" s="49"/>
+      <c r="BO29" s="49"/>
+      <c r="BP29" s="49"/>
+      <c r="BQ29" s="49"/>
+      <c r="BR29" s="49"/>
+      <c r="BS29" s="49"/>
+      <c r="BT29" s="49"/>
+      <c r="BU29" s="49"/>
+      <c r="BV29" s="49"/>
+      <c r="BW29" s="49"/>
+      <c r="BX29" s="49"/>
+      <c r="BY29" s="49"/>
+      <c r="BZ29" s="49"/>
+      <c r="CA29" s="49"/>
+      <c r="CB29" s="49"/>
+      <c r="CC29" s="49"/>
+      <c r="CD29" s="49"/>
+      <c r="CE29" s="49"/>
+      <c r="CF29" s="50"/>
+    </row>
+    <row r="30" spans="2:84">
+      <c r="B30" s="23"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="23"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="24"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="23"/>
+      <c r="W30" s="24"/>
+      <c r="X30" s="24"/>
+      <c r="Y30" s="24"/>
+      <c r="Z30" s="24"/>
+      <c r="AA30" s="24"/>
+      <c r="AB30" s="24"/>
+      <c r="AC30" s="24"/>
+      <c r="AD30" s="25"/>
+      <c r="AE30" s="23"/>
+      <c r="AF30" s="24"/>
+      <c r="AG30" s="24"/>
+      <c r="AH30" s="24"/>
+      <c r="AI30" s="24"/>
+      <c r="AJ30" s="24"/>
+      <c r="AK30" s="24"/>
+      <c r="AL30" s="24"/>
+      <c r="AM30" s="25"/>
+      <c r="AN30" s="23"/>
+      <c r="AO30" s="24"/>
+      <c r="AP30" s="24"/>
+      <c r="AQ30" s="24"/>
+      <c r="AR30" s="24"/>
+      <c r="AS30" s="24"/>
+      <c r="AT30" s="24"/>
+      <c r="AU30" s="24"/>
+      <c r="AV30" s="25"/>
+      <c r="AW30" s="23"/>
+      <c r="AX30" s="24"/>
+      <c r="AY30" s="25"/>
+      <c r="AZ30" s="23"/>
+      <c r="BA30" s="24"/>
+      <c r="BB30" s="25"/>
+      <c r="BC30" s="23"/>
+      <c r="BD30" s="24"/>
+      <c r="BE30" s="24"/>
+      <c r="BF30" s="24"/>
+      <c r="BG30" s="25"/>
+      <c r="BH30" s="23"/>
+      <c r="BI30" s="24"/>
+      <c r="BJ30" s="24"/>
+      <c r="BK30" s="24"/>
+      <c r="BL30" s="25"/>
+      <c r="BM30" s="48"/>
+      <c r="BN30" s="49"/>
+      <c r="BO30" s="49"/>
+      <c r="BP30" s="49"/>
+      <c r="BQ30" s="49"/>
+      <c r="BR30" s="49"/>
+      <c r="BS30" s="49"/>
+      <c r="BT30" s="49"/>
+      <c r="BU30" s="49"/>
+      <c r="BV30" s="49"/>
+      <c r="BW30" s="49"/>
+      <c r="BX30" s="49"/>
+      <c r="BY30" s="49"/>
+      <c r="BZ30" s="49"/>
+      <c r="CA30" s="49"/>
+      <c r="CB30" s="49"/>
+      <c r="CC30" s="49"/>
+      <c r="CD30" s="49"/>
+      <c r="CE30" s="49"/>
+      <c r="CF30" s="50"/>
+    </row>
+    <row r="31" spans="2:84">
+      <c r="B31" s="23"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="23"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+      <c r="T31" s="24"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="23"/>
+      <c r="W31" s="24"/>
+      <c r="X31" s="24"/>
+      <c r="Y31" s="24"/>
+      <c r="Z31" s="24"/>
+      <c r="AA31" s="24"/>
+      <c r="AB31" s="24"/>
+      <c r="AC31" s="24"/>
+      <c r="AD31" s="25"/>
+      <c r="AE31" s="23"/>
+      <c r="AF31" s="24"/>
+      <c r="AG31" s="24"/>
+      <c r="AH31" s="24"/>
+      <c r="AI31" s="24"/>
+      <c r="AJ31" s="24"/>
+      <c r="AK31" s="24"/>
+      <c r="AL31" s="24"/>
+      <c r="AM31" s="25"/>
+      <c r="AN31" s="23"/>
+      <c r="AO31" s="24"/>
+      <c r="AP31" s="24"/>
+      <c r="AQ31" s="24"/>
+      <c r="AR31" s="24"/>
+      <c r="AS31" s="24"/>
+      <c r="AT31" s="24"/>
+      <c r="AU31" s="24"/>
+      <c r="AV31" s="25"/>
+      <c r="AW31" s="23"/>
+      <c r="AX31" s="24"/>
+      <c r="AY31" s="25"/>
+      <c r="AZ31" s="23"/>
+      <c r="BA31" s="24"/>
+      <c r="BB31" s="25"/>
+      <c r="BC31" s="23"/>
+      <c r="BD31" s="24"/>
+      <c r="BE31" s="24"/>
+      <c r="BF31" s="24"/>
+      <c r="BG31" s="25"/>
+      <c r="BH31" s="23"/>
+      <c r="BI31" s="24"/>
+      <c r="BJ31" s="24"/>
+      <c r="BK31" s="24"/>
+      <c r="BL31" s="25"/>
+      <c r="BM31" s="48"/>
+      <c r="BN31" s="49"/>
+      <c r="BO31" s="49"/>
+      <c r="BP31" s="49"/>
+      <c r="BQ31" s="49"/>
+      <c r="BR31" s="49"/>
+      <c r="BS31" s="49"/>
+      <c r="BT31" s="49"/>
+      <c r="BU31" s="49"/>
+      <c r="BV31" s="49"/>
+      <c r="BW31" s="49"/>
+      <c r="BX31" s="49"/>
+      <c r="BY31" s="49"/>
+      <c r="BZ31" s="49"/>
+      <c r="CA31" s="49"/>
+      <c r="CB31" s="49"/>
+      <c r="CC31" s="49"/>
+      <c r="CD31" s="49"/>
+      <c r="CE31" s="49"/>
+      <c r="CF31" s="50"/>
+    </row>
+    <row r="32" spans="2:84">
+      <c r="B32" s="23"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="23"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="25"/>
+      <c r="V32" s="23"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="24"/>
+      <c r="Z32" s="24"/>
+      <c r="AA32" s="24"/>
+      <c r="AB32" s="24"/>
+      <c r="AC32" s="24"/>
+      <c r="AD32" s="25"/>
+      <c r="AE32" s="23"/>
+      <c r="AF32" s="24"/>
+      <c r="AG32" s="24"/>
+      <c r="AH32" s="24"/>
+      <c r="AI32" s="24"/>
+      <c r="AJ32" s="24"/>
+      <c r="AK32" s="24"/>
+      <c r="AL32" s="24"/>
+      <c r="AM32" s="25"/>
+      <c r="AN32" s="23"/>
+      <c r="AO32" s="24"/>
+      <c r="AP32" s="24"/>
+      <c r="AQ32" s="24"/>
+      <c r="AR32" s="24"/>
+      <c r="AS32" s="24"/>
+      <c r="AT32" s="24"/>
+      <c r="AU32" s="24"/>
+      <c r="AV32" s="25"/>
+      <c r="AW32" s="23"/>
+      <c r="AX32" s="24"/>
+      <c r="AY32" s="25"/>
+      <c r="AZ32" s="23"/>
+      <c r="BA32" s="24"/>
+      <c r="BB32" s="25"/>
+      <c r="BC32" s="23"/>
+      <c r="BD32" s="24"/>
+      <c r="BE32" s="24"/>
+      <c r="BF32" s="24"/>
+      <c r="BG32" s="25"/>
+      <c r="BH32" s="23"/>
+      <c r="BI32" s="24"/>
+      <c r="BJ32" s="24"/>
+      <c r="BK32" s="24"/>
+      <c r="BL32" s="25"/>
+      <c r="BM32" s="48"/>
+      <c r="BN32" s="49"/>
+      <c r="BO32" s="49"/>
+      <c r="BP32" s="49"/>
+      <c r="BQ32" s="49"/>
+      <c r="BR32" s="49"/>
+      <c r="BS32" s="49"/>
+      <c r="BT32" s="49"/>
+      <c r="BU32" s="49"/>
+      <c r="BV32" s="49"/>
+      <c r="BW32" s="49"/>
+      <c r="BX32" s="49"/>
+      <c r="BY32" s="49"/>
+      <c r="BZ32" s="49"/>
+      <c r="CA32" s="49"/>
+      <c r="CB32" s="49"/>
+      <c r="CC32" s="49"/>
+      <c r="CD32" s="49"/>
+      <c r="CE32" s="49"/>
+      <c r="CF32" s="50"/>
+    </row>
+    <row r="33" spans="2:84">
+      <c r="B33" s="23"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="23"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="24"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="23"/>
+      <c r="W33" s="24"/>
+      <c r="X33" s="24"/>
+      <c r="Y33" s="24"/>
+      <c r="Z33" s="24"/>
+      <c r="AA33" s="24"/>
+      <c r="AB33" s="24"/>
+      <c r="AC33" s="24"/>
+      <c r="AD33" s="25"/>
+      <c r="AE33" s="23"/>
+      <c r="AF33" s="24"/>
+      <c r="AG33" s="24"/>
+      <c r="AH33" s="24"/>
+      <c r="AI33" s="24"/>
+      <c r="AJ33" s="24"/>
+      <c r="AK33" s="24"/>
+      <c r="AL33" s="24"/>
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="23"/>
+      <c r="AO33" s="24"/>
+      <c r="AP33" s="24"/>
+      <c r="AQ33" s="24"/>
+      <c r="AR33" s="24"/>
+      <c r="AS33" s="24"/>
+      <c r="AT33" s="24"/>
+      <c r="AU33" s="24"/>
+      <c r="AV33" s="25"/>
+      <c r="AW33" s="23"/>
+      <c r="AX33" s="24"/>
+      <c r="AY33" s="25"/>
+      <c r="AZ33" s="23"/>
+      <c r="BA33" s="24"/>
+      <c r="BB33" s="25"/>
+      <c r="BC33" s="23"/>
+      <c r="BD33" s="24"/>
+      <c r="BE33" s="24"/>
+      <c r="BF33" s="24"/>
+      <c r="BG33" s="25"/>
+      <c r="BH33" s="23"/>
+      <c r="BI33" s="24"/>
+      <c r="BJ33" s="24"/>
+      <c r="BK33" s="24"/>
+      <c r="BL33" s="25"/>
+      <c r="BM33" s="48"/>
+      <c r="BN33" s="49"/>
+      <c r="BO33" s="49"/>
+      <c r="BP33" s="49"/>
+      <c r="BQ33" s="49"/>
+      <c r="BR33" s="49"/>
+      <c r="BS33" s="49"/>
+      <c r="BT33" s="49"/>
+      <c r="BU33" s="49"/>
+      <c r="BV33" s="49"/>
+      <c r="BW33" s="49"/>
+      <c r="BX33" s="49"/>
+      <c r="BY33" s="49"/>
+      <c r="BZ33" s="49"/>
+      <c r="CA33" s="49"/>
+      <c r="CB33" s="49"/>
+      <c r="CC33" s="49"/>
+      <c r="CD33" s="49"/>
+      <c r="CE33" s="49"/>
+      <c r="CF33" s="50"/>
+    </row>
+    <row r="34" spans="2:84">
+      <c r="B34" s="23"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="23"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="23"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="24"/>
+      <c r="Y34" s="24"/>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="24"/>
+      <c r="AB34" s="24"/>
+      <c r="AC34" s="24"/>
+      <c r="AD34" s="25"/>
+      <c r="AE34" s="23"/>
+      <c r="AF34" s="24"/>
+      <c r="AG34" s="24"/>
+      <c r="AH34" s="24"/>
+      <c r="AI34" s="24"/>
+      <c r="AJ34" s="24"/>
+      <c r="AK34" s="24"/>
+      <c r="AL34" s="24"/>
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="23"/>
+      <c r="AO34" s="24"/>
+      <c r="AP34" s="24"/>
+      <c r="AQ34" s="24"/>
+      <c r="AR34" s="24"/>
+      <c r="AS34" s="24"/>
+      <c r="AT34" s="24"/>
+      <c r="AU34" s="24"/>
+      <c r="AV34" s="25"/>
+      <c r="AW34" s="23"/>
+      <c r="AX34" s="24"/>
+      <c r="AY34" s="25"/>
+      <c r="AZ34" s="23"/>
+      <c r="BA34" s="24"/>
+      <c r="BB34" s="25"/>
+      <c r="BC34" s="23"/>
+      <c r="BD34" s="24"/>
+      <c r="BE34" s="24"/>
+      <c r="BF34" s="24"/>
+      <c r="BG34" s="25"/>
+      <c r="BH34" s="23"/>
+      <c r="BI34" s="24"/>
+      <c r="BJ34" s="24"/>
+      <c r="BK34" s="24"/>
+      <c r="BL34" s="25"/>
+      <c r="BM34" s="48"/>
+      <c r="BN34" s="49"/>
+      <c r="BO34" s="49"/>
+      <c r="BP34" s="49"/>
+      <c r="BQ34" s="49"/>
+      <c r="BR34" s="49"/>
+      <c r="BS34" s="49"/>
+      <c r="BT34" s="49"/>
+      <c r="BU34" s="49"/>
+      <c r="BV34" s="49"/>
+      <c r="BW34" s="49"/>
+      <c r="BX34" s="49"/>
+      <c r="BY34" s="49"/>
+      <c r="BZ34" s="49"/>
+      <c r="CA34" s="49"/>
+      <c r="CB34" s="49"/>
+      <c r="CC34" s="49"/>
+      <c r="CD34" s="49"/>
+      <c r="CE34" s="49"/>
+      <c r="CF34" s="50"/>
+    </row>
+    <row r="35" spans="2:84">
+      <c r="B35" s="23"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="23"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
+      <c r="AB35" s="24"/>
+      <c r="AC35" s="24"/>
+      <c r="AD35" s="25"/>
+      <c r="AE35" s="23"/>
+      <c r="AF35" s="24"/>
+      <c r="AG35" s="24"/>
+      <c r="AH35" s="24"/>
+      <c r="AI35" s="24"/>
+      <c r="AJ35" s="24"/>
+      <c r="AK35" s="24"/>
+      <c r="AL35" s="24"/>
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="23"/>
+      <c r="AO35" s="24"/>
+      <c r="AP35" s="24"/>
+      <c r="AQ35" s="24"/>
+      <c r="AR35" s="24"/>
+      <c r="AS35" s="24"/>
+      <c r="AT35" s="24"/>
+      <c r="AU35" s="24"/>
+      <c r="AV35" s="25"/>
+      <c r="AW35" s="23"/>
+      <c r="AX35" s="24"/>
+      <c r="AY35" s="25"/>
+      <c r="AZ35" s="23"/>
+      <c r="BA35" s="24"/>
+      <c r="BB35" s="25"/>
+      <c r="BC35" s="23"/>
+      <c r="BD35" s="24"/>
+      <c r="BE35" s="24"/>
+      <c r="BF35" s="24"/>
+      <c r="BG35" s="25"/>
+      <c r="BH35" s="23"/>
+      <c r="BI35" s="24"/>
+      <c r="BJ35" s="24"/>
+      <c r="BK35" s="24"/>
+      <c r="BL35" s="25"/>
+      <c r="BM35" s="48"/>
+      <c r="BN35" s="49"/>
+      <c r="BO35" s="49"/>
+      <c r="BP35" s="49"/>
+      <c r="BQ35" s="49"/>
+      <c r="BR35" s="49"/>
+      <c r="BS35" s="49"/>
+      <c r="BT35" s="49"/>
+      <c r="BU35" s="49"/>
+      <c r="BV35" s="49"/>
+      <c r="BW35" s="49"/>
+      <c r="BX35" s="49"/>
+      <c r="BY35" s="49"/>
+      <c r="BZ35" s="49"/>
+      <c r="CA35" s="49"/>
+      <c r="CB35" s="49"/>
+      <c r="CC35" s="49"/>
+      <c r="CD35" s="49"/>
+      <c r="CE35" s="49"/>
+      <c r="CF35" s="50"/>
+    </row>
+    <row r="36" spans="2:84">
+      <c r="B36" s="23"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="23"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="24"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="25"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="24"/>
+      <c r="X36" s="24"/>
+      <c r="Y36" s="24"/>
+      <c r="Z36" s="24"/>
+      <c r="AA36" s="24"/>
+      <c r="AB36" s="24"/>
+      <c r="AC36" s="24"/>
+      <c r="AD36" s="25"/>
+      <c r="AE36" s="23"/>
+      <c r="AF36" s="24"/>
+      <c r="AG36" s="24"/>
+      <c r="AH36" s="24"/>
+      <c r="AI36" s="24"/>
+      <c r="AJ36" s="24"/>
+      <c r="AK36" s="24"/>
+      <c r="AL36" s="24"/>
+      <c r="AM36" s="25"/>
+      <c r="AN36" s="23"/>
+      <c r="AO36" s="24"/>
+      <c r="AP36" s="24"/>
+      <c r="AQ36" s="24"/>
+      <c r="AR36" s="24"/>
+      <c r="AS36" s="24"/>
+      <c r="AT36" s="24"/>
+      <c r="AU36" s="24"/>
+      <c r="AV36" s="25"/>
+      <c r="AW36" s="23"/>
+      <c r="AX36" s="24"/>
+      <c r="AY36" s="25"/>
+      <c r="AZ36" s="23"/>
+      <c r="BA36" s="24"/>
+      <c r="BB36" s="25"/>
+      <c r="BC36" s="23"/>
+      <c r="BD36" s="24"/>
+      <c r="BE36" s="24"/>
+      <c r="BF36" s="24"/>
+      <c r="BG36" s="25"/>
+      <c r="BH36" s="23"/>
+      <c r="BI36" s="24"/>
+      <c r="BJ36" s="24"/>
+      <c r="BK36" s="24"/>
+      <c r="BL36" s="25"/>
+      <c r="BM36" s="48"/>
+      <c r="BN36" s="49"/>
+      <c r="BO36" s="49"/>
+      <c r="BP36" s="49"/>
+      <c r="BQ36" s="49"/>
+      <c r="BR36" s="49"/>
+      <c r="BS36" s="49"/>
+      <c r="BT36" s="49"/>
+      <c r="BU36" s="49"/>
+      <c r="BV36" s="49"/>
+      <c r="BW36" s="49"/>
+      <c r="BX36" s="49"/>
+      <c r="BY36" s="49"/>
+      <c r="BZ36" s="49"/>
+      <c r="CA36" s="49"/>
+      <c r="CB36" s="49"/>
+      <c r="CC36" s="49"/>
+      <c r="CD36" s="49"/>
+      <c r="CE36" s="49"/>
+      <c r="CF36" s="50"/>
+    </row>
+    <row r="37" spans="2:84">
+      <c r="B37" s="23"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="23"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="24"/>
+      <c r="T37" s="24"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="23"/>
+      <c r="W37" s="24"/>
+      <c r="X37" s="24"/>
+      <c r="Y37" s="24"/>
+      <c r="Z37" s="24"/>
+      <c r="AA37" s="24"/>
+      <c r="AB37" s="24"/>
+      <c r="AC37" s="24"/>
+      <c r="AD37" s="25"/>
+      <c r="AE37" s="23"/>
+      <c r="AF37" s="24"/>
+      <c r="AG37" s="24"/>
+      <c r="AH37" s="24"/>
+      <c r="AI37" s="24"/>
+      <c r="AJ37" s="24"/>
+      <c r="AK37" s="24"/>
+      <c r="AL37" s="24"/>
+      <c r="AM37" s="25"/>
+      <c r="AN37" s="23"/>
+      <c r="AO37" s="24"/>
+      <c r="AP37" s="24"/>
+      <c r="AQ37" s="24"/>
+      <c r="AR37" s="24"/>
+      <c r="AS37" s="24"/>
+      <c r="AT37" s="24"/>
+      <c r="AU37" s="24"/>
+      <c r="AV37" s="25"/>
+      <c r="AW37" s="23"/>
+      <c r="AX37" s="24"/>
+      <c r="AY37" s="25"/>
+      <c r="AZ37" s="23"/>
+      <c r="BA37" s="24"/>
+      <c r="BB37" s="25"/>
+      <c r="BC37" s="23"/>
+      <c r="BD37" s="24"/>
+      <c r="BE37" s="24"/>
+      <c r="BF37" s="24"/>
+      <c r="BG37" s="25"/>
+      <c r="BH37" s="23"/>
+      <c r="BI37" s="24"/>
+      <c r="BJ37" s="24"/>
+      <c r="BK37" s="24"/>
+      <c r="BL37" s="25"/>
+      <c r="BM37" s="48"/>
+      <c r="BN37" s="49"/>
+      <c r="BO37" s="49"/>
+      <c r="BP37" s="49"/>
+      <c r="BQ37" s="49"/>
+      <c r="BR37" s="49"/>
+      <c r="BS37" s="49"/>
+      <c r="BT37" s="49"/>
+      <c r="BU37" s="49"/>
+      <c r="BV37" s="49"/>
+      <c r="BW37" s="49"/>
+      <c r="BX37" s="49"/>
+      <c r="BY37" s="49"/>
+      <c r="BZ37" s="49"/>
+      <c r="CA37" s="49"/>
+      <c r="CB37" s="49"/>
+      <c r="CC37" s="49"/>
+      <c r="CD37" s="49"/>
+      <c r="CE37" s="49"/>
+      <c r="CF37" s="50"/>
+    </row>
+    <row r="38" spans="2:84">
+      <c r="B38" s="23"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="23"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="23"/>
+      <c r="W38" s="24"/>
+      <c r="X38" s="24"/>
+      <c r="Y38" s="24"/>
+      <c r="Z38" s="24"/>
+      <c r="AA38" s="24"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="24"/>
+      <c r="AD38" s="25"/>
+      <c r="AE38" s="23"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
+      <c r="AH38" s="24"/>
+      <c r="AI38" s="24"/>
+      <c r="AJ38" s="24"/>
+      <c r="AK38" s="24"/>
+      <c r="AL38" s="24"/>
+      <c r="AM38" s="25"/>
+      <c r="AN38" s="23"/>
+      <c r="AO38" s="24"/>
+      <c r="AP38" s="24"/>
+      <c r="AQ38" s="24"/>
+      <c r="AR38" s="24"/>
+      <c r="AS38" s="24"/>
+      <c r="AT38" s="24"/>
+      <c r="AU38" s="24"/>
+      <c r="AV38" s="25"/>
+      <c r="AW38" s="23"/>
+      <c r="AX38" s="24"/>
+      <c r="AY38" s="25"/>
+      <c r="AZ38" s="23"/>
+      <c r="BA38" s="24"/>
+      <c r="BB38" s="25"/>
+      <c r="BC38" s="23"/>
+      <c r="BD38" s="24"/>
+      <c r="BE38" s="24"/>
+      <c r="BF38" s="24"/>
+      <c r="BG38" s="25"/>
+      <c r="BH38" s="23"/>
+      <c r="BI38" s="24"/>
+      <c r="BJ38" s="24"/>
+      <c r="BK38" s="24"/>
+      <c r="BL38" s="25"/>
+      <c r="BM38" s="48"/>
+      <c r="BN38" s="49"/>
+      <c r="BO38" s="49"/>
+      <c r="BP38" s="49"/>
+      <c r="BQ38" s="49"/>
+      <c r="BR38" s="49"/>
+      <c r="BS38" s="49"/>
+      <c r="BT38" s="49"/>
+      <c r="BU38" s="49"/>
+      <c r="BV38" s="49"/>
+      <c r="BW38" s="49"/>
+      <c r="BX38" s="49"/>
+      <c r="BY38" s="49"/>
+      <c r="BZ38" s="49"/>
+      <c r="CA38" s="49"/>
+      <c r="CB38" s="49"/>
+      <c r="CC38" s="49"/>
+      <c r="CD38" s="49"/>
+      <c r="CE38" s="49"/>
+      <c r="CF38" s="50"/>
+    </row>
+    <row r="39" spans="2:84">
+      <c r="B39" s="23"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="23"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="23"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="24"/>
+      <c r="AD39" s="25"/>
+      <c r="AE39" s="23"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24"/>
+      <c r="AH39" s="24"/>
+      <c r="AI39" s="24"/>
+      <c r="AJ39" s="24"/>
+      <c r="AK39" s="24"/>
+      <c r="AL39" s="24"/>
+      <c r="AM39" s="25"/>
+      <c r="AN39" s="23"/>
+      <c r="AO39" s="24"/>
+      <c r="AP39" s="24"/>
+      <c r="AQ39" s="24"/>
+      <c r="AR39" s="24"/>
+      <c r="AS39" s="24"/>
+      <c r="AT39" s="24"/>
+      <c r="AU39" s="24"/>
+      <c r="AV39" s="25"/>
+      <c r="AW39" s="23"/>
+      <c r="AX39" s="24"/>
+      <c r="AY39" s="25"/>
+      <c r="AZ39" s="23"/>
+      <c r="BA39" s="24"/>
+      <c r="BB39" s="25"/>
+      <c r="BC39" s="23"/>
+      <c r="BD39" s="24"/>
+      <c r="BE39" s="24"/>
+      <c r="BF39" s="24"/>
+      <c r="BG39" s="25"/>
+      <c r="BH39" s="23"/>
+      <c r="BI39" s="24"/>
+      <c r="BJ39" s="24"/>
+      <c r="BK39" s="24"/>
+      <c r="BL39" s="25"/>
+      <c r="BM39" s="48"/>
+      <c r="BN39" s="49"/>
+      <c r="BO39" s="49"/>
+      <c r="BP39" s="49"/>
+      <c r="BQ39" s="49"/>
+      <c r="BR39" s="49"/>
+      <c r="BS39" s="49"/>
+      <c r="BT39" s="49"/>
+      <c r="BU39" s="49"/>
+      <c r="BV39" s="49"/>
+      <c r="BW39" s="49"/>
+      <c r="BX39" s="49"/>
+      <c r="BY39" s="49"/>
+      <c r="BZ39" s="49"/>
+      <c r="CA39" s="49"/>
+      <c r="CB39" s="49"/>
+      <c r="CC39" s="49"/>
+      <c r="CD39" s="49"/>
+      <c r="CE39" s="49"/>
+      <c r="CF39" s="50"/>
+    </row>
+    <row r="40" spans="2:84">
+      <c r="B40" s="23"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="23"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="25"/>
+      <c r="V40" s="23"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
+      <c r="Y40" s="24"/>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="24"/>
+      <c r="AD40" s="25"/>
+      <c r="AE40" s="23"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
+      <c r="AH40" s="24"/>
+      <c r="AI40" s="24"/>
+      <c r="AJ40" s="24"/>
+      <c r="AK40" s="24"/>
+      <c r="AL40" s="24"/>
+      <c r="AM40" s="25"/>
+      <c r="AN40" s="23"/>
+      <c r="AO40" s="24"/>
+      <c r="AP40" s="24"/>
+      <c r="AQ40" s="24"/>
+      <c r="AR40" s="24"/>
+      <c r="AS40" s="24"/>
+      <c r="AT40" s="24"/>
+      <c r="AU40" s="24"/>
+      <c r="AV40" s="25"/>
+      <c r="AW40" s="23"/>
+      <c r="AX40" s="24"/>
+      <c r="AY40" s="25"/>
+      <c r="AZ40" s="23"/>
+      <c r="BA40" s="24"/>
+      <c r="BB40" s="25"/>
+      <c r="BC40" s="23"/>
+      <c r="BD40" s="24"/>
+      <c r="BE40" s="24"/>
+      <c r="BF40" s="24"/>
+      <c r="BG40" s="25"/>
+      <c r="BH40" s="23"/>
+      <c r="BI40" s="24"/>
+      <c r="BJ40" s="24"/>
+      <c r="BK40" s="24"/>
+      <c r="BL40" s="25"/>
+      <c r="BM40" s="48"/>
+      <c r="BN40" s="49"/>
+      <c r="BO40" s="49"/>
+      <c r="BP40" s="49"/>
+      <c r="BQ40" s="49"/>
+      <c r="BR40" s="49"/>
+      <c r="BS40" s="49"/>
+      <c r="BT40" s="49"/>
+      <c r="BU40" s="49"/>
+      <c r="BV40" s="49"/>
+      <c r="BW40" s="49"/>
+      <c r="BX40" s="49"/>
+      <c r="BY40" s="49"/>
+      <c r="BZ40" s="49"/>
+      <c r="CA40" s="49"/>
+      <c r="CB40" s="49"/>
+      <c r="CC40" s="49"/>
+      <c r="CD40" s="49"/>
+      <c r="CE40" s="49"/>
+      <c r="CF40" s="50"/>
+    </row>
+    <row r="41" spans="2:84">
+      <c r="B41" s="23"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="25"/>
+      <c r="M41" s="23"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
+      <c r="R41" s="24"/>
+      <c r="S41" s="24"/>
+      <c r="T41" s="24"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="23"/>
+      <c r="W41" s="24"/>
+      <c r="X41" s="24"/>
+      <c r="Y41" s="24"/>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="24"/>
+      <c r="AD41" s="25"/>
+      <c r="AE41" s="23"/>
+      <c r="AF41" s="24"/>
+      <c r="AG41" s="24"/>
+      <c r="AH41" s="24"/>
+      <c r="AI41" s="24"/>
+      <c r="AJ41" s="24"/>
+      <c r="AK41" s="24"/>
+      <c r="AL41" s="24"/>
+      <c r="AM41" s="25"/>
+      <c r="AN41" s="23"/>
+      <c r="AO41" s="24"/>
+      <c r="AP41" s="24"/>
+      <c r="AQ41" s="24"/>
+      <c r="AR41" s="24"/>
+      <c r="AS41" s="24"/>
+      <c r="AT41" s="24"/>
+      <c r="AU41" s="24"/>
+      <c r="AV41" s="25"/>
+      <c r="AW41" s="23"/>
+      <c r="AX41" s="24"/>
+      <c r="AY41" s="25"/>
+      <c r="AZ41" s="23"/>
+      <c r="BA41" s="24"/>
+      <c r="BB41" s="25"/>
+      <c r="BC41" s="23"/>
+      <c r="BD41" s="24"/>
+      <c r="BE41" s="24"/>
+      <c r="BF41" s="24"/>
+      <c r="BG41" s="25"/>
+      <c r="BH41" s="23"/>
+      <c r="BI41" s="24"/>
+      <c r="BJ41" s="24"/>
+      <c r="BK41" s="24"/>
+      <c r="BL41" s="25"/>
+      <c r="BM41" s="48"/>
+      <c r="BN41" s="49"/>
+      <c r="BO41" s="49"/>
+      <c r="BP41" s="49"/>
+      <c r="BQ41" s="49"/>
+      <c r="BR41" s="49"/>
+      <c r="BS41" s="49"/>
+      <c r="BT41" s="49"/>
+      <c r="BU41" s="49"/>
+      <c r="BV41" s="49"/>
+      <c r="BW41" s="49"/>
+      <c r="BX41" s="49"/>
+      <c r="BY41" s="49"/>
+      <c r="BZ41" s="49"/>
+      <c r="CA41" s="49"/>
+      <c r="CB41" s="49"/>
+      <c r="CC41" s="49"/>
+      <c r="CD41" s="49"/>
+      <c r="CE41" s="49"/>
+      <c r="CF41" s="50"/>
+    </row>
+    <row r="42" spans="2:84">
+      <c r="B42" s="23"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="25"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="S42" s="24"/>
+      <c r="T42" s="24"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="23"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="24"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="24"/>
+      <c r="AD42" s="25"/>
+      <c r="AE42" s="23"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
+      <c r="AH42" s="24"/>
+      <c r="AI42" s="24"/>
+      <c r="AJ42" s="24"/>
+      <c r="AK42" s="24"/>
+      <c r="AL42" s="24"/>
+      <c r="AM42" s="25"/>
+      <c r="AN42" s="23"/>
+      <c r="AO42" s="24"/>
+      <c r="AP42" s="24"/>
+      <c r="AQ42" s="24"/>
+      <c r="AR42" s="24"/>
+      <c r="AS42" s="24"/>
+      <c r="AT42" s="24"/>
+      <c r="AU42" s="24"/>
+      <c r="AV42" s="25"/>
+      <c r="AW42" s="23"/>
+      <c r="AX42" s="24"/>
+      <c r="AY42" s="25"/>
+      <c r="AZ42" s="23"/>
+      <c r="BA42" s="24"/>
+      <c r="BB42" s="25"/>
+      <c r="BC42" s="23"/>
+      <c r="BD42" s="24"/>
+      <c r="BE42" s="24"/>
+      <c r="BF42" s="24"/>
+      <c r="BG42" s="25"/>
+      <c r="BH42" s="23"/>
+      <c r="BI42" s="24"/>
+      <c r="BJ42" s="24"/>
+      <c r="BK42" s="24"/>
+      <c r="BL42" s="25"/>
+      <c r="BM42" s="48"/>
+      <c r="BN42" s="49"/>
+      <c r="BO42" s="49"/>
+      <c r="BP42" s="49"/>
+      <c r="BQ42" s="49"/>
+      <c r="BR42" s="49"/>
+      <c r="BS42" s="49"/>
+      <c r="BT42" s="49"/>
+      <c r="BU42" s="49"/>
+      <c r="BV42" s="49"/>
+      <c r="BW42" s="49"/>
+      <c r="BX42" s="49"/>
+      <c r="BY42" s="49"/>
+      <c r="BZ42" s="49"/>
+      <c r="CA42" s="49"/>
+      <c r="CB42" s="49"/>
+      <c r="CC42" s="49"/>
+      <c r="CD42" s="49"/>
+      <c r="CE42" s="49"/>
+      <c r="CF42" s="50"/>
+    </row>
+    <row r="43" spans="2:84">
+      <c r="B43" s="23"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="25"/>
+      <c r="M43" s="23"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="24"/>
+      <c r="Q43" s="24"/>
+      <c r="R43" s="24"/>
+      <c r="S43" s="24"/>
+      <c r="T43" s="24"/>
+      <c r="U43" s="25"/>
+      <c r="V43" s="23"/>
+      <c r="W43" s="24"/>
+      <c r="X43" s="24"/>
+      <c r="Y43" s="24"/>
+      <c r="Z43" s="24"/>
+      <c r="AA43" s="24"/>
+      <c r="AB43" s="24"/>
+      <c r="AC43" s="24"/>
+      <c r="AD43" s="25"/>
+      <c r="AE43" s="23"/>
+      <c r="AF43" s="24"/>
+      <c r="AG43" s="24"/>
+      <c r="AH43" s="24"/>
+      <c r="AI43" s="24"/>
+      <c r="AJ43" s="24"/>
+      <c r="AK43" s="24"/>
+      <c r="AL43" s="24"/>
+      <c r="AM43" s="25"/>
+      <c r="AN43" s="23"/>
+      <c r="AO43" s="24"/>
+      <c r="AP43" s="24"/>
+      <c r="AQ43" s="24"/>
+      <c r="AR43" s="24"/>
+      <c r="AS43" s="24"/>
+      <c r="AT43" s="24"/>
+      <c r="AU43" s="24"/>
+      <c r="AV43" s="25"/>
+      <c r="AW43" s="23"/>
+      <c r="AX43" s="24"/>
+      <c r="AY43" s="25"/>
+      <c r="AZ43" s="23"/>
+      <c r="BA43" s="24"/>
+      <c r="BB43" s="25"/>
+      <c r="BC43" s="23"/>
+      <c r="BD43" s="24"/>
+      <c r="BE43" s="24"/>
+      <c r="BF43" s="24"/>
+      <c r="BG43" s="25"/>
+      <c r="BH43" s="23"/>
+      <c r="BI43" s="24"/>
+      <c r="BJ43" s="24"/>
+      <c r="BK43" s="24"/>
+      <c r="BL43" s="25"/>
+      <c r="BM43" s="48"/>
+      <c r="BN43" s="49"/>
+      <c r="BO43" s="49"/>
+      <c r="BP43" s="49"/>
+      <c r="BQ43" s="49"/>
+      <c r="BR43" s="49"/>
+      <c r="BS43" s="49"/>
+      <c r="BT43" s="49"/>
+      <c r="BU43" s="49"/>
+      <c r="BV43" s="49"/>
+      <c r="BW43" s="49"/>
+      <c r="BX43" s="49"/>
+      <c r="BY43" s="49"/>
+      <c r="BZ43" s="49"/>
+      <c r="CA43" s="49"/>
+      <c r="CB43" s="49"/>
+      <c r="CC43" s="49"/>
+      <c r="CD43" s="49"/>
+      <c r="CE43" s="49"/>
+      <c r="CF43" s="50"/>
+    </row>
+    <row r="44" spans="2:84">
+      <c r="B44" s="23"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="25"/>
+      <c r="M44" s="23"/>
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="S44" s="24"/>
+      <c r="T44" s="24"/>
+      <c r="U44" s="25"/>
+      <c r="V44" s="23"/>
+      <c r="W44" s="24"/>
+      <c r="X44" s="24"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="24"/>
+      <c r="AD44" s="25"/>
+      <c r="AE44" s="23"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="24"/>
+      <c r="AJ44" s="24"/>
+      <c r="AK44" s="24"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="25"/>
+      <c r="AN44" s="23"/>
+      <c r="AO44" s="24"/>
+      <c r="AP44" s="24"/>
+      <c r="AQ44" s="24"/>
+      <c r="AR44" s="24"/>
+      <c r="AS44" s="24"/>
+      <c r="AT44" s="24"/>
+      <c r="AU44" s="24"/>
+      <c r="AV44" s="25"/>
+      <c r="AW44" s="23"/>
+      <c r="AX44" s="24"/>
+      <c r="AY44" s="25"/>
+      <c r="AZ44" s="23"/>
+      <c r="BA44" s="24"/>
+      <c r="BB44" s="25"/>
+      <c r="BC44" s="23"/>
+      <c r="BD44" s="24"/>
+      <c r="BE44" s="24"/>
+      <c r="BF44" s="24"/>
+      <c r="BG44" s="25"/>
+      <c r="BH44" s="23"/>
+      <c r="BI44" s="24"/>
+      <c r="BJ44" s="24"/>
+      <c r="BK44" s="24"/>
+      <c r="BL44" s="25"/>
+      <c r="BM44" s="48"/>
+      <c r="BN44" s="49"/>
+      <c r="BO44" s="49"/>
+      <c r="BP44" s="49"/>
+      <c r="BQ44" s="49"/>
+      <c r="BR44" s="49"/>
+      <c r="BS44" s="49"/>
+      <c r="BT44" s="49"/>
+      <c r="BU44" s="49"/>
+      <c r="BV44" s="49"/>
+      <c r="BW44" s="49"/>
+      <c r="BX44" s="49"/>
+      <c r="BY44" s="49"/>
+      <c r="BZ44" s="49"/>
+      <c r="CA44" s="49"/>
+      <c r="CB44" s="49"/>
+      <c r="CC44" s="49"/>
+      <c r="CD44" s="49"/>
+      <c r="CE44" s="49"/>
+      <c r="CF44" s="50"/>
+    </row>
+    <row r="45" spans="2:84">
+      <c r="B45" s="23"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="25"/>
+      <c r="M45" s="23"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="24"/>
+      <c r="R45" s="24"/>
+      <c r="S45" s="24"/>
+      <c r="T45" s="24"/>
+      <c r="U45" s="25"/>
+      <c r="V45" s="23"/>
+      <c r="W45" s="24"/>
+      <c r="X45" s="24"/>
+      <c r="Y45" s="24"/>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="24"/>
+      <c r="AB45" s="24"/>
+      <c r="AC45" s="24"/>
+      <c r="AD45" s="25"/>
+      <c r="AE45" s="23"/>
+      <c r="AF45" s="24"/>
+      <c r="AG45" s="24"/>
+      <c r="AH45" s="24"/>
+      <c r="AI45" s="24"/>
+      <c r="AJ45" s="24"/>
+      <c r="AK45" s="24"/>
+      <c r="AL45" s="24"/>
+      <c r="AM45" s="25"/>
+      <c r="AN45" s="23"/>
+      <c r="AO45" s="24"/>
+      <c r="AP45" s="24"/>
+      <c r="AQ45" s="24"/>
+      <c r="AR45" s="24"/>
+      <c r="AS45" s="24"/>
+      <c r="AT45" s="24"/>
+      <c r="AU45" s="24"/>
+      <c r="AV45" s="25"/>
+      <c r="AW45" s="23"/>
+      <c r="AX45" s="24"/>
+      <c r="AY45" s="25"/>
+      <c r="AZ45" s="23"/>
+      <c r="BA45" s="24"/>
+      <c r="BB45" s="25"/>
+      <c r="BC45" s="23"/>
+      <c r="BD45" s="24"/>
+      <c r="BE45" s="24"/>
+      <c r="BF45" s="24"/>
+      <c r="BG45" s="25"/>
+      <c r="BH45" s="23"/>
+      <c r="BI45" s="24"/>
+      <c r="BJ45" s="24"/>
+      <c r="BK45" s="24"/>
+      <c r="BL45" s="25"/>
+      <c r="BM45" s="48"/>
+      <c r="BN45" s="49"/>
+      <c r="BO45" s="49"/>
+      <c r="BP45" s="49"/>
+      <c r="BQ45" s="49"/>
+      <c r="BR45" s="49"/>
+      <c r="BS45" s="49"/>
+      <c r="BT45" s="49"/>
+      <c r="BU45" s="49"/>
+      <c r="BV45" s="49"/>
+      <c r="BW45" s="49"/>
+      <c r="BX45" s="49"/>
+      <c r="BY45" s="49"/>
+      <c r="BZ45" s="49"/>
+      <c r="CA45" s="49"/>
+      <c r="CB45" s="49"/>
+      <c r="CC45" s="49"/>
+      <c r="CD45" s="49"/>
+      <c r="CE45" s="49"/>
+      <c r="CF45" s="50"/>
+    </row>
+    <row r="90" s="42" customFormat="1"/>
+    <row r="91" s="42" customFormat="1"/>
+  </sheetData>
+  <mergeCells count="418">
+    <mergeCell ref="BM13:CF13"/>
+    <mergeCell ref="BM14:CF15"/>
+    <mergeCell ref="BM9:CF9"/>
+    <mergeCell ref="BM10:CF10"/>
+    <mergeCell ref="BM11:CF11"/>
+    <mergeCell ref="BM12:CF12"/>
+    <mergeCell ref="BM16:CF16"/>
+    <mergeCell ref="AN13:AV13"/>
+    <mergeCell ref="V10:AD13"/>
+    <mergeCell ref="AW13:AY13"/>
+    <mergeCell ref="BC13:BG13"/>
+    <mergeCell ref="BH13:BL13"/>
+    <mergeCell ref="AZ13:BB13"/>
+    <mergeCell ref="B2:AQ2"/>
+    <mergeCell ref="D7:L8"/>
+    <mergeCell ref="M7:U8"/>
+    <mergeCell ref="AE10:AM11"/>
+    <mergeCell ref="V14:AD15"/>
+    <mergeCell ref="AE13:AM13"/>
+    <mergeCell ref="AN45:AV45"/>
+    <mergeCell ref="AW45:AY45"/>
+    <mergeCell ref="AZ45:BB45"/>
+    <mergeCell ref="BC45:BG45"/>
+    <mergeCell ref="BH45:BL45"/>
+    <mergeCell ref="BM45:CF45"/>
+    <mergeCell ref="AW44:AY44"/>
+    <mergeCell ref="AZ44:BB44"/>
+    <mergeCell ref="BC44:BG44"/>
+    <mergeCell ref="BH44:BL44"/>
+    <mergeCell ref="BM44:CF44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:L45"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="V45:AD45"/>
+    <mergeCell ref="AE45:AM45"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:L44"/>
+    <mergeCell ref="M44:U44"/>
+    <mergeCell ref="V44:AD44"/>
+    <mergeCell ref="AE44:AM44"/>
+    <mergeCell ref="AN44:AV44"/>
+    <mergeCell ref="AN43:AV43"/>
+    <mergeCell ref="AW43:AY43"/>
+    <mergeCell ref="AZ43:BB43"/>
+    <mergeCell ref="BC43:BG43"/>
+    <mergeCell ref="BH43:BL43"/>
+    <mergeCell ref="BM43:CF43"/>
+    <mergeCell ref="AW42:AY42"/>
+    <mergeCell ref="AZ42:BB42"/>
+    <mergeCell ref="BC42:BG42"/>
+    <mergeCell ref="BH42:BL42"/>
+    <mergeCell ref="BM42:CF42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:L43"/>
+    <mergeCell ref="M43:U43"/>
+    <mergeCell ref="V43:AD43"/>
+    <mergeCell ref="AE43:AM43"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="D42:L42"/>
+    <mergeCell ref="M42:U42"/>
+    <mergeCell ref="V42:AD42"/>
+    <mergeCell ref="AE42:AM42"/>
+    <mergeCell ref="AN42:AV42"/>
+    <mergeCell ref="AN41:AV41"/>
+    <mergeCell ref="AW41:AY41"/>
+    <mergeCell ref="AZ41:BB41"/>
+    <mergeCell ref="BC41:BG41"/>
+    <mergeCell ref="BH41:BL41"/>
+    <mergeCell ref="BM41:CF41"/>
+    <mergeCell ref="AW40:AY40"/>
+    <mergeCell ref="AZ40:BB40"/>
+    <mergeCell ref="BC40:BG40"/>
+    <mergeCell ref="BH40:BL40"/>
+    <mergeCell ref="BM40:CF40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:L41"/>
+    <mergeCell ref="M41:U41"/>
+    <mergeCell ref="V41:AD41"/>
+    <mergeCell ref="AE41:AM41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="D40:L40"/>
+    <mergeCell ref="M40:U40"/>
+    <mergeCell ref="V40:AD40"/>
+    <mergeCell ref="AE40:AM40"/>
+    <mergeCell ref="AN40:AV40"/>
+    <mergeCell ref="AN39:AV39"/>
+    <mergeCell ref="AW39:AY39"/>
+    <mergeCell ref="AZ39:BB39"/>
+    <mergeCell ref="BC39:BG39"/>
+    <mergeCell ref="BH39:BL39"/>
+    <mergeCell ref="BM39:CF39"/>
+    <mergeCell ref="AW38:AY38"/>
+    <mergeCell ref="AZ38:BB38"/>
+    <mergeCell ref="BC38:BG38"/>
+    <mergeCell ref="BH38:BL38"/>
+    <mergeCell ref="BM38:CF38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:L39"/>
+    <mergeCell ref="M39:U39"/>
+    <mergeCell ref="V39:AD39"/>
+    <mergeCell ref="AE39:AM39"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="D38:L38"/>
+    <mergeCell ref="M38:U38"/>
+    <mergeCell ref="V38:AD38"/>
+    <mergeCell ref="AE38:AM38"/>
+    <mergeCell ref="AN38:AV38"/>
+    <mergeCell ref="AN37:AV37"/>
+    <mergeCell ref="AW37:AY37"/>
+    <mergeCell ref="AZ37:BB37"/>
+    <mergeCell ref="BC37:BG37"/>
+    <mergeCell ref="BH37:BL37"/>
+    <mergeCell ref="BM37:CF37"/>
+    <mergeCell ref="AW36:AY36"/>
+    <mergeCell ref="AZ36:BB36"/>
+    <mergeCell ref="BC36:BG36"/>
+    <mergeCell ref="BH36:BL36"/>
+    <mergeCell ref="BM36:CF36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:L37"/>
+    <mergeCell ref="M37:U37"/>
+    <mergeCell ref="V37:AD37"/>
+    <mergeCell ref="AE37:AM37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:L36"/>
+    <mergeCell ref="M36:U36"/>
+    <mergeCell ref="V36:AD36"/>
+    <mergeCell ref="AE36:AM36"/>
+    <mergeCell ref="AN36:AV36"/>
+    <mergeCell ref="AN35:AV35"/>
+    <mergeCell ref="AW35:AY35"/>
+    <mergeCell ref="AZ35:BB35"/>
+    <mergeCell ref="BC35:BG35"/>
+    <mergeCell ref="BH35:BL35"/>
+    <mergeCell ref="BM35:CF35"/>
+    <mergeCell ref="AW34:AY34"/>
+    <mergeCell ref="AZ34:BB34"/>
+    <mergeCell ref="BC34:BG34"/>
+    <mergeCell ref="BH34:BL34"/>
+    <mergeCell ref="BM34:CF34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="D35:L35"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="V35:AD35"/>
+    <mergeCell ref="AE35:AM35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="D34:L34"/>
+    <mergeCell ref="M34:U34"/>
+    <mergeCell ref="V34:AD34"/>
+    <mergeCell ref="AE34:AM34"/>
+    <mergeCell ref="AN34:AV34"/>
+    <mergeCell ref="AN33:AV33"/>
+    <mergeCell ref="AW33:AY33"/>
+    <mergeCell ref="AZ33:BB33"/>
+    <mergeCell ref="BC33:BG33"/>
+    <mergeCell ref="BH33:BL33"/>
+    <mergeCell ref="BM33:CF33"/>
+    <mergeCell ref="AW32:AY32"/>
+    <mergeCell ref="AZ32:BB32"/>
+    <mergeCell ref="BC32:BG32"/>
+    <mergeCell ref="BH32:BL32"/>
+    <mergeCell ref="BM32:CF32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:L33"/>
+    <mergeCell ref="M33:U33"/>
+    <mergeCell ref="V33:AD33"/>
+    <mergeCell ref="AE33:AM33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:L32"/>
+    <mergeCell ref="M32:U32"/>
+    <mergeCell ref="V32:AD32"/>
+    <mergeCell ref="AE32:AM32"/>
+    <mergeCell ref="AN32:AV32"/>
+    <mergeCell ref="AN31:AV31"/>
+    <mergeCell ref="AW31:AY31"/>
+    <mergeCell ref="AZ31:BB31"/>
+    <mergeCell ref="BC31:BG31"/>
+    <mergeCell ref="BH31:BL31"/>
+    <mergeCell ref="BM31:CF31"/>
+    <mergeCell ref="AW30:AY30"/>
+    <mergeCell ref="AZ30:BB30"/>
+    <mergeCell ref="BC30:BG30"/>
+    <mergeCell ref="BH30:BL30"/>
+    <mergeCell ref="BM30:CF30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:L31"/>
+    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="V31:AD31"/>
+    <mergeCell ref="AE31:AM31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:L30"/>
+    <mergeCell ref="M30:U30"/>
+    <mergeCell ref="V30:AD30"/>
+    <mergeCell ref="AE30:AM30"/>
+    <mergeCell ref="AN30:AV30"/>
+    <mergeCell ref="AN29:AV29"/>
+    <mergeCell ref="AW29:AY29"/>
+    <mergeCell ref="AZ29:BB29"/>
+    <mergeCell ref="BC29:BG29"/>
+    <mergeCell ref="BH29:BL29"/>
+    <mergeCell ref="BM29:CF29"/>
+    <mergeCell ref="AW28:AY28"/>
+    <mergeCell ref="AZ28:BB28"/>
+    <mergeCell ref="BC28:BG28"/>
+    <mergeCell ref="BH28:BL28"/>
+    <mergeCell ref="BM28:CF28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:L29"/>
+    <mergeCell ref="M29:U29"/>
+    <mergeCell ref="V29:AD29"/>
+    <mergeCell ref="AE29:AM29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:L28"/>
+    <mergeCell ref="M28:U28"/>
+    <mergeCell ref="V28:AD28"/>
+    <mergeCell ref="AE28:AM28"/>
+    <mergeCell ref="AN28:AV28"/>
+    <mergeCell ref="AN27:AV27"/>
+    <mergeCell ref="AW27:AY27"/>
+    <mergeCell ref="AZ27:BB27"/>
+    <mergeCell ref="BC27:BG27"/>
+    <mergeCell ref="BH27:BL27"/>
+    <mergeCell ref="BM27:CF27"/>
+    <mergeCell ref="AW26:AY26"/>
+    <mergeCell ref="AZ26:BB26"/>
+    <mergeCell ref="BC26:BG26"/>
+    <mergeCell ref="BH26:BL26"/>
+    <mergeCell ref="BM26:CF26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:L27"/>
+    <mergeCell ref="M27:U27"/>
+    <mergeCell ref="V27:AD27"/>
+    <mergeCell ref="AE27:AM27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:L26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="V26:AD26"/>
+    <mergeCell ref="AE26:AM26"/>
+    <mergeCell ref="AN26:AV26"/>
+    <mergeCell ref="AN25:AV25"/>
+    <mergeCell ref="AW25:AY25"/>
+    <mergeCell ref="AZ25:BB25"/>
+    <mergeCell ref="BC25:BG25"/>
+    <mergeCell ref="BH25:BL25"/>
+    <mergeCell ref="BM25:CF25"/>
+    <mergeCell ref="AW24:AY24"/>
+    <mergeCell ref="AZ24:BB24"/>
+    <mergeCell ref="BC24:BG24"/>
+    <mergeCell ref="BH24:BL24"/>
+    <mergeCell ref="BM24:CF24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:L25"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="V25:AD25"/>
+    <mergeCell ref="AE25:AM25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:L24"/>
+    <mergeCell ref="M24:U24"/>
+    <mergeCell ref="V24:AD24"/>
+    <mergeCell ref="AE24:AM24"/>
+    <mergeCell ref="AN24:AV24"/>
+    <mergeCell ref="AN23:AV23"/>
+    <mergeCell ref="AW23:AY23"/>
+    <mergeCell ref="AZ23:BB23"/>
+    <mergeCell ref="BC23:BG23"/>
+    <mergeCell ref="BH23:BL23"/>
+    <mergeCell ref="BM23:CF23"/>
+    <mergeCell ref="AW22:AY22"/>
+    <mergeCell ref="AZ22:BB22"/>
+    <mergeCell ref="BC22:BG22"/>
+    <mergeCell ref="BH22:BL22"/>
+    <mergeCell ref="BM22:CF22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:L23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="V23:AD23"/>
+    <mergeCell ref="AE23:AM23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:L22"/>
+    <mergeCell ref="M22:U22"/>
+    <mergeCell ref="V22:AD22"/>
+    <mergeCell ref="AE22:AM22"/>
+    <mergeCell ref="AN22:AV22"/>
+    <mergeCell ref="AN21:AV21"/>
+    <mergeCell ref="AW21:AY21"/>
+    <mergeCell ref="AZ21:BB21"/>
+    <mergeCell ref="BC21:BG21"/>
+    <mergeCell ref="BH21:BL21"/>
+    <mergeCell ref="BM21:CF21"/>
+    <mergeCell ref="AW20:AY20"/>
+    <mergeCell ref="AZ20:BB20"/>
+    <mergeCell ref="BC20:BG20"/>
+    <mergeCell ref="BH20:BL20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:L21"/>
+    <mergeCell ref="V21:AD21"/>
+    <mergeCell ref="AE21:AM21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:L20"/>
+    <mergeCell ref="AN20:AV20"/>
+    <mergeCell ref="AE18:AM20"/>
+    <mergeCell ref="V17:AD20"/>
+    <mergeCell ref="M16:U21"/>
+    <mergeCell ref="AN19:AV19"/>
+    <mergeCell ref="AW19:AY19"/>
+    <mergeCell ref="AZ19:BB19"/>
+    <mergeCell ref="BC19:BG19"/>
+    <mergeCell ref="BH19:BL19"/>
+    <mergeCell ref="BM18:CF20"/>
+    <mergeCell ref="AW18:AY18"/>
+    <mergeCell ref="AZ18:BB18"/>
+    <mergeCell ref="BC18:BG18"/>
+    <mergeCell ref="BH18:BL18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:L19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="AN18:AV18"/>
+    <mergeCell ref="AN17:AV17"/>
+    <mergeCell ref="AW17:AY17"/>
+    <mergeCell ref="AZ17:BB17"/>
+    <mergeCell ref="BC17:BG17"/>
+    <mergeCell ref="BH17:BL17"/>
+    <mergeCell ref="BM17:CF17"/>
+    <mergeCell ref="AW16:AY16"/>
+    <mergeCell ref="AZ16:BB16"/>
+    <mergeCell ref="BC16:BG16"/>
+    <mergeCell ref="BH16:BL16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="AE17:AM17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:L16"/>
+    <mergeCell ref="V16:AD16"/>
+    <mergeCell ref="AE16:AM16"/>
+    <mergeCell ref="AN16:AV16"/>
+    <mergeCell ref="AN15:AV15"/>
+    <mergeCell ref="AW15:AY15"/>
+    <mergeCell ref="AZ15:BB15"/>
+    <mergeCell ref="BC15:BG15"/>
+    <mergeCell ref="BH15:BL15"/>
+    <mergeCell ref="AW14:AY14"/>
+    <mergeCell ref="AZ14:BB14"/>
+    <mergeCell ref="BC14:BG14"/>
+    <mergeCell ref="BH14:BL14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="AE15:AM15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:L14"/>
+    <mergeCell ref="AE14:AM14"/>
+    <mergeCell ref="AN14:AV14"/>
+    <mergeCell ref="M9:U15"/>
+    <mergeCell ref="AN12:AV12"/>
+    <mergeCell ref="AW12:AY12"/>
+    <mergeCell ref="AZ12:BB12"/>
+    <mergeCell ref="BC12:BG12"/>
+    <mergeCell ref="BH12:BL12"/>
+    <mergeCell ref="AW11:AY11"/>
+    <mergeCell ref="AZ11:BB11"/>
+    <mergeCell ref="BC11:BG11"/>
+    <mergeCell ref="BH11:BL11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="AE12:AM12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="AN11:AV11"/>
+    <mergeCell ref="AN10:AV10"/>
+    <mergeCell ref="AW10:AY10"/>
+    <mergeCell ref="AZ10:BB10"/>
+    <mergeCell ref="BC10:BG10"/>
+    <mergeCell ref="BH10:BL10"/>
+    <mergeCell ref="AW9:AY9"/>
+    <mergeCell ref="AZ9:BB9"/>
+    <mergeCell ref="BC9:BG9"/>
+    <mergeCell ref="BH9:BL9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="V9:AD9"/>
+    <mergeCell ref="AE9:AM9"/>
+    <mergeCell ref="AN9:AV9"/>
+    <mergeCell ref="AN8:AV8"/>
+    <mergeCell ref="AW8:AY8"/>
+    <mergeCell ref="AZ8:BB8"/>
+    <mergeCell ref="BC8:BG8"/>
+    <mergeCell ref="BH8:BL8"/>
+    <mergeCell ref="BM8:CF8"/>
+    <mergeCell ref="AW7:AY7"/>
+    <mergeCell ref="AZ7:BB7"/>
+    <mergeCell ref="BC7:BG7"/>
+    <mergeCell ref="BH7:BL7"/>
+    <mergeCell ref="BM7:CF7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="V8:AD8"/>
+    <mergeCell ref="AE8:AM8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="V7:AD7"/>
+    <mergeCell ref="AE7:AM7"/>
+    <mergeCell ref="AN7:AV7"/>
+    <mergeCell ref="BC5:BG6"/>
+    <mergeCell ref="BH5:BL6"/>
+    <mergeCell ref="BM5:CF6"/>
+    <mergeCell ref="AE6:AM6"/>
+    <mergeCell ref="AN6:AV6"/>
+    <mergeCell ref="D5:AV5"/>
+    <mergeCell ref="AW5:AY6"/>
+    <mergeCell ref="AZ5:BB6"/>
+    <mergeCell ref="D6:L6"/>
+    <mergeCell ref="M6:U6"/>
+    <mergeCell ref="V6:AD6"/>
+    <mergeCell ref="N4:S4"/>
+    <mergeCell ref="B5:C6"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="E4:I4"/>
+    <mergeCell ref="K4:M4"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="63" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{058AF5FD-8286-4BD8-BF85-E6D41CC9EEAB}">
-  <dimension ref="H1:P1"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" orientation="portrait" r:id="rId1"/>
-  <colBreaks count="1" manualBreakCount="1">
-    <brk id="41" max="54" man="1"/>
-  </colBreaks>
+  <pageSetup paperSize="9" scale="39" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>